--- a/ovk-dom-banya/release-nvk/И05.09.26-НВК.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-nvk/И05.09.26-НВК.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -504,7 +504,7 @@
       <c r="A3" s="1" t="inlineStr"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>1. Водопровод В1 (ввод) и подводка полива КХ-8</t>
+          <t>1. Водопровод В1 (ввод), подводка полива КХ-8 и линия к беседке</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>
@@ -568,12 +568,12 @@
         </is>
       </c>
       <c r="G5" s="1" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>КХ-8н, подводка полива до КП-1</t>
+          <t>КХ-8н до КП-1 (2,5 м), В1-Бс к беседке (41,0 м)</t>
         </is>
       </c>
     </row>
@@ -812,12 +812,12 @@
         </is>
       </c>
       <c r="G13" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>стык с КХ-8 (ВК) у фундамента, вход в кран КП-1</t>
+          <t>стык с КХ-8 (ВК) у фундамента, КП-1 (2), колонка КБ</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Колодец полимерный Ø400 с крышкой (газонный), H ≈ 0,92 м</t>
+          <t>Тройник компрессионный ПЭ 25</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
@@ -848,7 +848,7 @@
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr">
         <is>
-          <t>КП-1 (лист 8, узел 7)</t>
+          <t>КП-1: ответвление к беседке</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 20 латунный с полусгоном для шланга</t>
+          <t>Колодец полимерный Ø400, H ≈ 1,08 м, люк Т (C250) на опорном кольце — зона заезда</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
@@ -879,7 +879,7 @@
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr">
         <is>
-          <t>КП-1: полив, беседка</t>
+          <t>КП-1 (лист 8, узел 7)</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой спускной Ду 15</t>
+          <t>Кран шаровой Ду 20 латунный с полусгоном для шланга</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -905,12 +905,12 @@
         </is>
       </c>
       <c r="G16" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr">
         <is>
-          <t>КП-1: слив на зиму</t>
+          <t>КП-1: полив; ответвление к беседке</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Лента сигнальная «Осторожно! Водопровод»</t>
+          <t>Колонка садовая (стойка) с краном Ду 15, высота 0,8 м, сезонная</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -932,73 +932,93 @@
       <c r="E17" s="1" t="inlineStr"/>
       <c r="F17" s="1" t="inlineStr">
         <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="1" t="inlineStr"/>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>КБ у беседки (лист 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Футляр из трубы ПНД Ø63</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr"/>
+      <c r="E18" s="1" t="inlineStr"/>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
           <t>м</t>
         </is>
       </c>
-      <c r="G17" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="H17" s="1" t="inlineStr"/>
-      <c r="I17" s="1" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr"/>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>2. Канализация бытовая К1</t>
-        </is>
-      </c>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
-      <c r="E18" s="1" t="n"/>
-      <c r="F18" s="1" t="n"/>
-      <c r="G18" s="1" t="n"/>
-      <c r="H18" s="1" t="n"/>
-      <c r="I18" s="1" t="n"/>
+      <c r="G18" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="H18" s="1" t="inlineStr"/>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>В1-Бс в зоне заезда вдоль восточного забора</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Труба ПП гофрированная двухслойная SN8 Ø110 с раструбом и уплотнительным кольцом</t>
+          <t>Кран шаровой спускной Ду 15</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32413-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr"/>
       <c r="E19" s="1" t="inlineStr"/>
       <c r="F19" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G19" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr">
         <is>
-          <t>выпуски К1-1н, К1-бн</t>
+          <t>КП-1: слив на зиму</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Труба ПП гофрированная двухслойная SN8 Ø160 с раструбом и уплотнительным кольцом</t>
+          <t>Лента сигнальная «Осторожно! Водопровод»</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32413-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr"/>
@@ -1009,45 +1029,25 @@
         </is>
       </c>
       <c r="G20" s="1" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H20" s="1" t="inlineStr"/>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>сеть бани К1-б1…К1-б3</t>
-        </is>
-      </c>
+      <c r="I20" s="1" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Отвод ПП Ø110, 15°</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr"/>
-      <c r="E21" s="1" t="inlineStr"/>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G21" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="1" t="inlineStr"/>
-      <c r="I21" s="1" t="inlineStr">
-        <is>
-          <t>стык с выпуском К1-1 (ВК), угол — по месту</t>
-        </is>
-      </c>
+      <c r="A21" s="1" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>2. Канализация бытовая К1</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="n"/>
+      <c r="D21" s="1" t="n"/>
+      <c r="E21" s="1" t="n"/>
+      <c r="F21" s="1" t="n"/>
+      <c r="G21" s="1" t="n"/>
+      <c r="H21" s="1" t="n"/>
+      <c r="I21" s="1" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1055,28 +1055,28 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Колодец канализационный полимерный Ø630 с проточным лотком (приём Ø110, выход Ø160), шахтой гофр. Ø400 телескопической и люком, H = 0,81 м</t>
+          <t>Труба ПП гофрированная двухслойная SN8 Ø110 с раструбом и уплотнительным кольцом</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32413-2013</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr"/>
       <c r="E22" s="1" t="inlineStr"/>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G22" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H22" s="1" t="inlineStr"/>
       <c r="I22" s="1" t="inlineStr">
         <is>
-          <t>КК-1 (лист 8, узел 4)</t>
+          <t>выпуски К1-1н, К1-бн</t>
         </is>
       </c>
     </row>
@@ -1086,28 +1086,28 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Колодец канализационный полимерный Ø630 с проточным лотком (проход Ø160, поворот 90°), шахтой гофр. Ø400 телескопической и люком, H = 1,16 м</t>
+          <t>Труба ПП гофрированная двухслойная SN8 Ø160 с раструбом и уплотнительным кольцом</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32413-2013</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr"/>
       <c r="E23" s="1" t="inlineStr"/>
       <c r="F23" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G23" s="1" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr">
         <is>
-          <t>КК-2 (лист 8, узел 4)</t>
+          <t>сеть бани К1-б1…К1-б3</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Колодец канализационный полимерный Ø630 с проточным лотком (проход Ø160, поворот 81°), шахтой гофр. Ø400 телескопической и люком, H = 1,34 м</t>
+          <t>Отвод ПП Ø110, 15°</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
@@ -1138,7 +1138,7 @@
       <c r="H24" s="1" t="inlineStr"/>
       <c r="I24" s="1" t="inlineStr">
         <is>
-          <t>КК-3 (лист 8, узел 4)</t>
+          <t>стык с выпуском К1-1 (ВК), угол — по месту</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø110</t>
+          <t>Колодец канализационный полимерный Ø630 с проточным лотком (приём Ø110, выход Ø160), шахтой гофр. Ø400 телескопической, H = 0,96 м, люк Л</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
@@ -1169,7 +1169,7 @@
       <c r="H25" s="1" t="inlineStr"/>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>врезка К1-1н в ДК5-018 (узел 3)</t>
+          <t>КК-1 (лист 8, узел 4)</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø160</t>
+          <t>Колодец канализационный полимерный Ø630 с проточным лотком (проход Ø160, поворот 90°), шахтой гофр. Ø400 телескопической, H = 1,19 м, люк Т (C250) на опорном кольце — зона заезда</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
@@ -1200,7 +1200,7 @@
       <c r="H26" s="1" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr">
         <is>
-          <t>врезка К1-б3 в ДК5-018 (узел 3)</t>
+          <t>КК-2 (лист 8, узел 4)</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Лента сигнальная «Осторожно! Канализация»</t>
+          <t>Колодец канализационный полимерный Ø630 с проточным лотком (проход Ø160, поворот 81°), шахтой гофр. Ø400 телескопической, H = 1,44 м, люк Т (C250) на опорном кольце — зона заезда</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
@@ -1222,73 +1222,93 @@
       <c r="E27" s="1" t="inlineStr"/>
       <c r="F27" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G27" s="1" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="H27" s="1" t="inlineStr"/>
-      <c r="I27" s="1" t="inlineStr"/>
+      <c r="I27" s="1" t="inlineStr">
+        <is>
+          <t>КК-3 (лист 8, узел 4)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr"/>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>3. Канализация ливневая К2. Сборный колодец КЛ-1</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="n"/>
-      <c r="D28" s="1" t="n"/>
-      <c r="E28" s="1" t="n"/>
-      <c r="F28" s="1" t="n"/>
-      <c r="G28" s="1" t="n"/>
-      <c r="H28" s="1" t="n"/>
-      <c r="I28" s="1" t="n"/>
+      <c r="A28" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø110</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr"/>
+      <c r="E28" s="1" t="inlineStr"/>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="1" t="inlineStr"/>
+      <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t>врезка К1-1н в ДК5-018 (узел 3)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Труба ПП гофрированная двухслойная SN8 Ø110 с раструбом и уплотнительным кольцом</t>
+          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø160</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32413-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr"/>
       <c r="E29" s="1" t="inlineStr"/>
       <c r="F29" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G29" s="1" t="n">
-        <v>164</v>
+        <v>1</v>
       </c>
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr">
         <is>
-          <t>кольца К2 дома и бани, транзит, выпуск лотка гаража</t>
+          <t>врезка К1-б3 в ДК5-018 (узел 3)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Труба напорная ПЭ 100 SDR17 63×3,8</t>
+          <t>Лента сигнальная «Осторожно! Канализация»</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 18599-2001</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr"/>
@@ -1299,45 +1319,25 @@
         </is>
       </c>
       <c r="G30" s="1" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="H30" s="1" t="inlineStr"/>
-      <c r="I30" s="1" t="inlineStr">
-        <is>
-          <t>выпуск КЛ-1 → выпуск ЛК Ø63</t>
-        </is>
-      </c>
+      <c r="I30" s="1" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Муфта электросварная ПЭ 100 Ø63</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr"/>
-      <c r="E31" s="1" t="inlineStr"/>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G31" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="1" t="inlineStr"/>
-      <c r="I31" s="1" t="inlineStr">
-        <is>
-          <t>стык с выпуском ЛК (после шурфа)</t>
-        </is>
-      </c>
+      <c r="A31" s="1" t="inlineStr"/>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>3. Канализация ливневая К2. Сборный колодец КЛ-1</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="n"/>
+      <c r="D31" s="1" t="n"/>
+      <c r="E31" s="1" t="n"/>
+      <c r="F31" s="1" t="n"/>
+      <c r="G31" s="1" t="n"/>
+      <c r="H31" s="1" t="n"/>
+      <c r="I31" s="1" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -1345,28 +1345,28 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП Ø110, 45°</t>
+          <t>Труба ПП гофрированная двухслойная SN8 Ø110 с раструбом и уплотнительным кольцом</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32413-2013</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr"/>
       <c r="E32" s="1" t="inlineStr"/>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G32" s="1" t="n">
-        <v>36</v>
+        <v>165</v>
       </c>
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr">
         <is>
-          <t>углы колец (по 2 на угол), транзит, выпуск гаража; выпуски водостоков — по 2</t>
+          <t>кольца К2 дома и бани, транзит, выпуск лотка гаража</t>
         </is>
       </c>
     </row>
@@ -1376,28 +1376,28 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП Ø110, 90°</t>
+          <t>Труба напорная ПЭ 100 SDR17 63×3,8</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 18599-2001</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr"/>
       <c r="E33" s="1" t="inlineStr"/>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G33" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr">
         <is>
-          <t>слияние полуколец, приём транзита бани</t>
+          <t>выпуск КЛ-1 → выпуск ЛК Ø63</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП Ø110 косой 45°</t>
+          <t>Муфта электросварная ПЭ 100 Ø63</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
@@ -1423,12 +1423,12 @@
         </is>
       </c>
       <c r="G34" s="1" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>выпуски водостоков (8, ориентировочно — по привязке воронок) и лотка гаража</t>
+          <t>стык с выпуском ЛК (после шурфа)</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Футляр (гильза) из трубы ПП Ø160, L = 0,6 м — закладная в край плиты</t>
+          <t>Отвод ПП Ø110, 45°</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
@@ -1454,12 +1454,12 @@
         </is>
       </c>
       <c r="G35" s="1" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>выпуски водостоков (узел 9), ориентировочно; закладка — при бетонировании (КР)</t>
+          <t>углы колец и вводов в КЛ-1 (по 2 на угол), транзит, выпуск гаража; выпуски водостоков — по 2</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Плита днища ПН15</t>
+          <t>Тройник ПП Ø110, 90°</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 8020-2016</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr"/>
@@ -1485,12 +1485,12 @@
         </is>
       </c>
       <c r="G36" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1 (лист 8, узел 2)</t>
+          <t>слияние полуколец бани, приём транзита бани</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Кольцо стеновое КС15.9</t>
+          <t>Тройник ПП Ø110 косой 45°</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 8020-2016</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr"/>
@@ -1516,12 +1516,12 @@
         </is>
       </c>
       <c r="G37" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1</t>
+          <t>выпуски водостоков (8, ориентировочно — по привязке воронок) и лотка гаража</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Кольцо стеновое КС15.6</t>
+          <t>Футляр (гильза) из трубы ПП Ø160, L = 0,6 м — закладная в край плиты</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 8020-2016</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr"/>
@@ -1547,12 +1547,12 @@
         </is>
       </c>
       <c r="G38" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1</t>
+          <t>выпуски водостоков (узел 9), ориентировочно; закладка — при бетонировании (КР)</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Плита перекрытия 1ПП15-1</t>
+          <t>Плита днища ПН15</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
@@ -1583,7 +1583,7 @@
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1</t>
+          <t>КЛ-1 (лист 8, узел 2)</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Кольцо стеновое КС7.3 (горловина)</t>
+          <t>Кольцо стеновое КС15.9</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Люк чугунный лёгкий Л (А15)</t>
+          <t>Кольцо стеновое КС15.6</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 3634-2019</t>
+          <t>ГОСТ 8020-2016</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr"/>
@@ -1645,7 +1645,7 @@
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1; в зоне проезда — Т (С250)</t>
+          <t>КЛ-1</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Скобы ходовые</t>
+          <t>Плита перекрытия 1ПП15-1</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
@@ -1671,12 +1671,12 @@
         </is>
       </c>
       <c r="G42" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1, шаг 0,3 м</t>
+          <t>КЛ-1</t>
         </is>
       </c>
     </row>
@@ -1686,28 +1686,28 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Мастика битумная для наружной гидроизоляции колец, 2 слоя</t>
+          <t>Кольцо стеновое КС7.3 (горловина)</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 8020-2016</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr"/>
       <c r="E43" s="1" t="inlineStr"/>
       <c r="F43" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G43" s="1" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1, наружная поверхность</t>
+          <t>КЛ-1</t>
         </is>
       </c>
     </row>
@@ -1717,12 +1717,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø110</t>
+          <t>Люк чугунный тяжёлый Т (C250)</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 3634-2019</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr"/>
@@ -1733,12 +1733,12 @@
         </is>
       </c>
       <c r="G44" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1: К2-К, Др-К</t>
+          <t>КЛ-1 — в зоне заезда</t>
         </is>
       </c>
     </row>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø63</t>
+          <t>Скобы ходовые</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 8020-2016</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr"/>
@@ -1764,12 +1764,12 @@
         </is>
       </c>
       <c r="G45" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1: выпуск</t>
+          <t>КЛ-1, шаг 0,3 м</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный канализационный (захлопка) Ø110</t>
+          <t>Мастика битумная для наружной гидроизоляции колец, 2 слоя</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
@@ -1791,16 +1791,16 @@
       <c r="E46" s="1" t="inlineStr"/>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G46" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1: вход дренажа Др-К</t>
+          <t>КЛ-1, наружная поверхность</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Решётка-корзина из нержавеющей стали на входе выпуска Ø63</t>
+          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø110</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
@@ -1826,122 +1826,122 @@
         </is>
       </c>
       <c r="G47" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1</t>
+          <t>КЛ-1: К2-К, К2-Б, Др-К</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="inlineStr"/>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>4. Дренаж Др</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="n"/>
-      <c r="D48" s="1" t="n"/>
-      <c r="E48" s="1" t="n"/>
-      <c r="F48" s="1" t="n"/>
-      <c r="G48" s="1" t="n"/>
-      <c r="H48" s="1" t="n"/>
-      <c r="I48" s="1" t="n"/>
+      <c r="A48" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø63</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="inlineStr"/>
+      <c r="E48" s="1" t="inlineStr"/>
+      <c r="F48" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G48" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="1" t="inlineStr"/>
+      <c r="I48" s="1" t="inlineStr">
+        <is>
+          <t>КЛ-1: выпуск</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Труба дренажная гофрированная перфорированная Ø110 в фильтре из геотекстиля</t>
+          <t>Клапан обратный канализационный (захлопка) Ø110</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ Р 59249-2020 или ТУ изготовителя</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr"/>
       <c r="E49" s="1" t="inlineStr"/>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G49" s="1" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr">
         <is>
-          <t>кольца дренажа дома и бани</t>
+          <t>КЛ-1: вход дренажа Др-К</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Труба ПП гофрированная двухслойная SN8 Ø110 (без перфорации)</t>
+          <t>Решётка-корзина из нержавеющей стали на входе выпуска Ø63</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32413-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr"/>
       <c r="E50" s="1" t="inlineStr"/>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G50" s="1" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr">
         <is>
-          <t>транзит Др-Т, выход Др-К в КЛ-1</t>
+          <t>КЛ-1</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>45</v>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Колодец дренажный полимерный: шахта гофр. Ø315, днище, крышка</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr"/>
-      <c r="E51" s="1" t="inlineStr"/>
-      <c r="F51" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G51" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="H51" s="1" t="inlineStr"/>
-      <c r="I51" s="1" t="inlineStr">
-        <is>
-          <t>Др-1…Др-4, ДрБ-1…ДрБ-4 (лист 8, узел 5)</t>
-        </is>
-      </c>
+      <c r="A51" s="1" t="inlineStr"/>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>4. Дренаж Др</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="n"/>
+      <c r="D51" s="1" t="n"/>
+      <c r="E51" s="1" t="n"/>
+      <c r="F51" s="1" t="n"/>
+      <c r="G51" s="1" t="n"/>
+      <c r="H51" s="1" t="n"/>
+      <c r="I51" s="1" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная Ø315 для шахт дренажных колодцев</t>
+          <t>Труба дренажная гофрированная перфорированная Ø110 в фильтре из геотекстиля</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ Р 59249-2020 или ТУ изготовителя</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr"/>
@@ -1965,12 +1965,12 @@
         </is>
       </c>
       <c r="G52" s="1" t="n">
-        <v>14</v>
+        <v>150</v>
       </c>
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr">
         <is>
-          <t>H = 1,39…1,71 м, отстойная часть 0,3 м</t>
+          <t>кольца дренажа дома и бани</t>
         </is>
       </c>
     </row>
@@ -1980,252 +1980,376 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Уплотнитель резиновый для ввода трубы Ø110 в колодец Ø315</t>
+          <t>Труба ПП гофрированная двухслойная SN8 Ø110 (без перфорации)</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32413-2013</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr"/>
       <c r="E53" s="1" t="inlineStr"/>
       <c r="F53" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G53" s="1" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H53" s="1" t="inlineStr"/>
-      <c r="I53" s="1" t="inlineStr"/>
+      <c r="I53" s="1" t="inlineStr">
+        <is>
+          <t>транзит Др-Т, выход Др-К в КЛ-1</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="inlineStr"/>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>5. Материалы траншей и утепление</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="n"/>
-      <c r="D54" s="1" t="n"/>
-      <c r="E54" s="1" t="n"/>
-      <c r="F54" s="1" t="n"/>
-      <c r="G54" s="1" t="n"/>
-      <c r="H54" s="1" t="n"/>
-      <c r="I54" s="1" t="n"/>
+      <c r="A54" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Колодец дренажный полимерный: шахта гофр. Ø315, днище, крышка</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="inlineStr"/>
+      <c r="E54" s="1" t="inlineStr"/>
+      <c r="F54" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="H54" s="1" t="inlineStr"/>
+      <c r="I54" s="1" t="inlineStr">
+        <is>
+          <t>Др-1…Др-4, ДрБ-1…ДрБ-4 (лист 8, узел 5)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Песок средней крупности для основания и обсыпки труб и колодцев</t>
+          <t>Труба гофрированная Ø315 для шахт дренажных колодцев</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 8736-2014</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr"/>
       <c r="E55" s="1" t="inlineStr"/>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>м³</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G55" s="1" t="n">
-        <v>56.5</v>
+        <v>15</v>
       </c>
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr">
         <is>
-          <t>основание 100 мм, обсыпка 300 мм над трубой</t>
+          <t>H = 1,54…1,79 м, отстойная часть 0,3 м</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Щебень гранитный фракции 20–40 мм, промытый</t>
+          <t>Уплотнитель резиновый для ввода трубы Ø110 в колодец Ø315</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 8267-93</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr"/>
       <c r="E56" s="1" t="inlineStr"/>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>м³</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G56" s="1" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="H56" s="1" t="inlineStr"/>
-      <c r="I56" s="1" t="inlineStr">
-        <is>
-          <t>призма вокруг дренажа (узел 8), основание КЛ-1</t>
-        </is>
-      </c>
+      <c r="I56" s="1" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Геотекстиль иглопробивной 150–200 г/м²</t>
+          <t>Люк чугунный тяжёлый Т (C250) с опорным кольцом для колодца Ø315</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 3634-2019</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr"/>
       <c r="E57" s="1" t="inlineStr"/>
       <c r="F57" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G57" s="1" t="n">
-        <v>360</v>
+        <v>4</v>
       </c>
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr">
         <is>
-          <t>обёртка щебня, нахлёст 0,3 м</t>
+          <t>Др-1, Др-3, ДрБ-2, ДрБ-3 — в зоне заезда</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
-        <v>51</v>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Плиты ЭППС 50 мм, плотность не менее 35 кг/м³</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr"/>
-      <c r="E58" s="1" t="inlineStr"/>
-      <c r="F58" s="1" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="G58" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="H58" s="1" t="inlineStr"/>
-      <c r="I58" s="1" t="inlineStr">
-        <is>
-          <t>полоса 1,2 м над трубой на мелких участках (узел 6)</t>
-        </is>
-      </c>
+      <c r="A58" s="1" t="inlineStr"/>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>5. Материалы траншей и утепление</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="n"/>
+      <c r="D58" s="1" t="n"/>
+      <c r="E58" s="1" t="n"/>
+      <c r="F58" s="1" t="n"/>
+      <c r="G58" s="1" t="n"/>
+      <c r="H58" s="1" t="n"/>
+      <c r="I58" s="1" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="inlineStr"/>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>6. Не входит в НВК.СО</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="n"/>
-      <c r="D59" s="1" t="n"/>
-      <c r="E59" s="1" t="n"/>
-      <c r="F59" s="1" t="n"/>
-      <c r="G59" s="1" t="n"/>
-      <c r="H59" s="1" t="n"/>
-      <c r="I59" s="1" t="n"/>
+      <c r="A59" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Песок средней крупности для основания и обсыпки труб и колодцев, засыпки в зоне заезда</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>ГОСТ 8736-2014</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="inlineStr"/>
+      <c r="E59" s="1" t="inlineStr"/>
+      <c r="F59" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="G59" s="1" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="H59" s="1" t="inlineStr"/>
+      <c r="I59" s="1" t="inlineStr">
+        <is>
+          <t>основание 100 мм, обсыпка 300 мм; в зоне заезда — на всю глубину (77,4 м³)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Стояки внутренних водостоков в стенах, выпуски К1, ввод В1 и подводка КХ-8 до наружной грани фундамента, лоток гаража ЛГ-1 с пескоуловителем — И05.09.26-ВК.СО</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr"/>
+          <t>Щебень гранитный фракции 20–40 мм, промытый</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>ГОСТ 8267-93</t>
+        </is>
+      </c>
       <c r="D60" s="1" t="inlineStr"/>
       <c r="E60" s="1" t="inlineStr"/>
-      <c r="F60" s="1" t="inlineStr"/>
-      <c r="G60" s="1" t="inlineStr"/>
+      <c r="F60" s="1" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="G60" s="1" t="n">
+        <v>33</v>
+      </c>
       <c r="H60" s="1" t="inlineStr"/>
-      <c r="I60" s="1" t="inlineStr"/>
+      <c r="I60" s="1" t="inlineStr">
+        <is>
+          <t>призма вокруг дренажа (узел 8), основание КЛ-1</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Утеплённая отмостка, утепление торца плиты, футляры в фундаменте — КР/АР</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr"/>
+          <t>Геотекстиль иглопробивной 150–200 г/м²</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D61" s="1" t="inlineStr"/>
       <c r="E61" s="1" t="inlineStr"/>
-      <c r="F61" s="1" t="inlineStr"/>
-      <c r="G61" s="1" t="inlineStr"/>
+      <c r="F61" s="1" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="G61" s="1" t="n">
+        <v>360</v>
+      </c>
       <c r="H61" s="1" t="inlineStr"/>
-      <c r="I61" s="1" t="inlineStr"/>
+      <c r="I61" s="1" t="inlineStr">
+        <is>
+          <t>обёртка щебня, нахлёст 0,3 м</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Терморегулятор и питание греющего кабеля — ЭОМ</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr"/>
+          <t>Плиты ЭППС 50 мм, плотность не менее 35 кг/м³</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D62" s="1" t="inlineStr"/>
       <c r="E62" s="1" t="inlineStr"/>
-      <c r="F62" s="1" t="inlineStr"/>
-      <c r="G62" s="1" t="inlineStr"/>
+      <c r="F62" s="1" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="G62" s="1" t="n">
+        <v>2</v>
+      </c>
       <c r="H62" s="1" t="inlineStr"/>
-      <c r="I62" s="1" t="inlineStr"/>
+      <c r="I62" s="1" t="inlineStr">
+        <is>
+          <t>полоса 1,2 м над трубой на мелких участках (узел 6)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
-        <v>55</v>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>Автополив участка и водопровод беседки от КП-1 — по ландшафтному проекту</t>
-        </is>
-      </c>
-      <c r="C63" s="1" t="inlineStr"/>
-      <c r="D63" s="1" t="inlineStr"/>
-      <c r="E63" s="1" t="inlineStr"/>
-      <c r="F63" s="1" t="inlineStr"/>
-      <c r="G63" s="1" t="inlineStr"/>
-      <c r="H63" s="1" t="inlineStr"/>
-      <c r="I63" s="1" t="inlineStr"/>
+      <c r="A63" s="1" t="inlineStr"/>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>6. Не входит в НВК.СО</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="n"/>
+      <c r="D63" s="1" t="n"/>
+      <c r="E63" s="1" t="n"/>
+      <c r="F63" s="1" t="n"/>
+      <c r="G63" s="1" t="n"/>
+      <c r="H63" s="1" t="n"/>
+      <c r="I63" s="1" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Стояки внутренних водостоков в стенах, выпуски К1, ввод В1 и подводка КХ-8 до наружной грани фундамента, лоток гаража ЛГ-1 с пескоуловителем — И05.09.26-ВК.СО</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="inlineStr"/>
+      <c r="D64" s="1" t="inlineStr"/>
+      <c r="E64" s="1" t="inlineStr"/>
+      <c r="F64" s="1" t="inlineStr"/>
+      <c r="G64" s="1" t="inlineStr"/>
+      <c r="H64" s="1" t="inlineStr"/>
+      <c r="I64" s="1" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr">
+      <c r="A65" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Утеплённая отмостка, утепление торца плиты, футляры в фундаменте — КР/АР</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="inlineStr"/>
+      <c r="D65" s="1" t="inlineStr"/>
+      <c r="E65" s="1" t="inlineStr"/>
+      <c r="F65" s="1" t="inlineStr"/>
+      <c r="G65" s="1" t="inlineStr"/>
+      <c r="H65" s="1" t="inlineStr"/>
+      <c r="I65" s="1" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Терморегулятор и питание греющего кабеля — ЭОМ</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr"/>
+      <c r="D66" s="1" t="inlineStr"/>
+      <c r="E66" s="1" t="inlineStr"/>
+      <c r="F66" s="1" t="inlineStr"/>
+      <c r="G66" s="1" t="inlineStr"/>
+      <c r="H66" s="1" t="inlineStr"/>
+      <c r="I66" s="1" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Автополив участка от КП-1 — по ландшафтному проекту</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr"/>
+      <c r="D67" s="1" t="inlineStr"/>
+      <c r="E67" s="1" t="inlineStr"/>
+      <c r="F67" s="1" t="inlineStr"/>
+      <c r="G67" s="1" t="inlineStr"/>
+      <c r="H67" s="1" t="inlineStr"/>
+      <c r="I67" s="1" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
         <is>
           <t>Примечание — Допускается применение оборудования, изделий и материалов других изготовителей с техническими характеристиками не ниже указанных в настоящей спецификации.</t>
         </is>

--- a/ovk-dom-banya/release-nvk/И05.09.26-НВК.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-nvk/И05.09.26-НВК.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -858,7 +858,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Колодец полимерный Ø400, H ≈ 1,08 м, люк Т (C250) на опорном кольце — зона заезда</t>
+          <t>Отвод компрессионный ПЭ 25, 90°</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
@@ -874,12 +874,12 @@
         </is>
       </c>
       <c r="G15" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr">
         <is>
-          <t>КП-1 (лист 8, узел 7)</t>
+          <t>В1-Бс: повороты трассы (4) и подъём к колонке КБ (1)</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 20 латунный с полусгоном для шланга</t>
+          <t>Колодец полимерный Ø400, H ≈ 1,08 м, люк Т (C250) на опорном кольце — зона заезда</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -905,12 +905,12 @@
         </is>
       </c>
       <c r="G16" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr">
         <is>
-          <t>КП-1: полив; ответвление к беседке</t>
+          <t>КП-1 (лист 8, узел 7)</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Колонка садовая (стойка) с краном Ду 15, высота 0,8 м, сезонная</t>
+          <t>Кран шаровой Ду 20 латунный с полусгоном для шланга</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -936,12 +936,12 @@
         </is>
       </c>
       <c r="G17" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr">
         <is>
-          <t>КБ у беседки (лист 3)</t>
+          <t>КП-1: полив; ответвление к беседке</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Футляр из трубы ПНД Ø63</t>
+          <t>Колонка садовая (стойка) с краном Ду 15, высота 0,8 м, сезонная</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
@@ -963,16 +963,16 @@
       <c r="E18" s="1" t="inlineStr"/>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G18" s="1" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr">
         <is>
-          <t>В1-Бс в зоне заезда вдоль восточного забора</t>
+          <t>КБ у беседки (лист 3)</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой спускной Ду 15</t>
+          <t>Футляр из трубы ПНД Ø63</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
@@ -994,16 +994,16 @@
       <c r="E19" s="1" t="inlineStr"/>
       <c r="F19" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G19" s="1" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr">
         <is>
-          <t>КП-1: слив на зиму</t>
+          <t>В1-Бс (18,5 м: зона заезда, перемычка за теплотрассой, над К2-Т и К1-б1 — по 2 м в стороны), КХ-8н на всю длину (2,5 м); лист 3</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Лента сигнальная «Осторожно! Водопровод»</t>
+          <t>Кран шаровой спускной Ду 15</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
@@ -1025,60 +1025,60 @@
       <c r="E20" s="1" t="inlineStr"/>
       <c r="F20" s="1" t="inlineStr">
         <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="1" t="inlineStr"/>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>КП-1: слив на зиму</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Лента сигнальная «Осторожно! Водопровод»</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr"/>
+      <c r="E21" s="1" t="inlineStr"/>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
           <t>м</t>
         </is>
       </c>
-      <c r="G20" s="1" t="n">
+      <c r="G21" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="H20" s="1" t="inlineStr"/>
-      <c r="I20" s="1" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr"/>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="H21" s="1" t="inlineStr"/>
+      <c r="I21" s="1" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>2. Канализация бытовая К1</t>
         </is>
       </c>
-      <c r="C21" s="1" t="n"/>
-      <c r="D21" s="1" t="n"/>
-      <c r="E21" s="1" t="n"/>
-      <c r="F21" s="1" t="n"/>
-      <c r="G21" s="1" t="n"/>
-      <c r="H21" s="1" t="n"/>
-      <c r="I21" s="1" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Труба ПП гофрированная двухслойная SN8 Ø110 с раструбом и уплотнительным кольцом</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>ГОСТ 32413-2013</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr"/>
-      <c r="E22" s="1" t="inlineStr"/>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G22" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="H22" s="1" t="inlineStr"/>
-      <c r="I22" s="1" t="inlineStr">
-        <is>
-          <t>выпуски К1-1н, К1-бн</t>
-        </is>
-      </c>
+      <c r="C22" s="1" t="n"/>
+      <c r="D22" s="1" t="n"/>
+      <c r="E22" s="1" t="n"/>
+      <c r="F22" s="1" t="n"/>
+      <c r="G22" s="1" t="n"/>
+      <c r="H22" s="1" t="n"/>
+      <c r="I22" s="1" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Труба ПП гофрированная двухслойная SN8 Ø160 с раструбом и уплотнительным кольцом</t>
+          <t>Труба ПП гофрированная двухслойная SN8 Ø110 с раструбом и уплотнительным кольцом</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
@@ -1102,12 +1102,12 @@
         </is>
       </c>
       <c r="G23" s="1" t="n">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr">
         <is>
-          <t>сеть бани К1-б1…К1-б3</t>
+          <t>выпуски К1-1н, К1-бн</t>
         </is>
       </c>
     </row>
@@ -1117,28 +1117,28 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП Ø110, 15°</t>
+          <t>Труба ПП гофрированная двухслойная SN8 Ø160 с раструбом и уплотнительным кольцом</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32413-2013</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr"/>
       <c r="E24" s="1" t="inlineStr"/>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G24" s="1" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="H24" s="1" t="inlineStr"/>
       <c r="I24" s="1" t="inlineStr">
         <is>
-          <t>стык с выпуском К1-1 (ВК), угол — по месту</t>
+          <t>сеть бани К1-б1…К1-б3</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Колодец канализационный полимерный Ø630 с проточным лотком (приём Ø110, выход Ø160), шахтой гофр. Ø400 телескопической, H = 0,96 м, люк Л</t>
+          <t>Отвод ПП Ø110, 15°</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
@@ -1169,7 +1169,7 @@
       <c r="H25" s="1" t="inlineStr"/>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>КК-1 (лист 8, узел 4)</t>
+          <t>стык с выпуском К1-1 (ВК), угол — по месту</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Колодец канализационный полимерный Ø630 с проточным лотком (проход Ø160, поворот 90°), шахтой гофр. Ø400 телескопической, H = 1,19 м, люк Т (C250) на опорном кольце — зона заезда</t>
+          <t>Колодец канализационный полимерный Ø630 с проточным лотком (приём Ø110, выход Ø160), шахтой гофр. Ø400 телескопической, H = 0,96 м, люк Л</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
@@ -1200,7 +1200,7 @@
       <c r="H26" s="1" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr">
         <is>
-          <t>КК-2 (лист 8, узел 4)</t>
+          <t>КК-1 (лист 8, узел 4)</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Колодец канализационный полимерный Ø630 с проточным лотком (проход Ø160, поворот 81°), шахтой гофр. Ø400 телескопической, H = 1,44 м, люк Т (C250) на опорном кольце — зона заезда</t>
+          <t>Колодец канализационный полимерный Ø630 с проточным лотком (проход Ø160, поворот 90°), шахтой гофр. Ø400 телескопической, H = 1,19 м, люк Т (C250) на опорном кольце — зона заезда</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
@@ -1231,7 +1231,7 @@
       <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr">
         <is>
-          <t>КК-3 (лист 8, узел 4)</t>
+          <t>КК-2 (лист 8, узел 4)</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø110</t>
+          <t>Колодец канализационный полимерный Ø630 с проточным лотком (проход Ø160, поворот 81°), шахтой гофр. Ø400 телескопической, H = 1,44 м, люк Т (C250) на опорном кольце — зона заезда</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
@@ -1262,7 +1262,7 @@
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>врезка К1-1н в ДК5-018 (узел 3)</t>
+          <t>КК-3 (лист 8, узел 4)</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø160</t>
+          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø110</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
@@ -1293,7 +1293,7 @@
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr">
         <is>
-          <t>врезка К1-б3 в ДК5-018 (узел 3)</t>
+          <t>врезка К1-1н в ДК5-018 (узел 3)</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Лента сигнальная «Осторожно! Канализация»</t>
+          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø160</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
@@ -1315,60 +1315,60 @@
       <c r="E30" s="1" t="inlineStr"/>
       <c r="F30" s="1" t="inlineStr">
         <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1" t="inlineStr"/>
+      <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t>врезка К1-б3 в ДК5-018 (узел 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Лента сигнальная «Осторожно! Канализация»</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="inlineStr"/>
+      <c r="E31" s="1" t="inlineStr"/>
+      <c r="F31" s="1" t="inlineStr">
+        <is>
           <t>м</t>
         </is>
       </c>
-      <c r="G30" s="1" t="n">
+      <c r="G31" s="1" t="n">
         <v>69</v>
       </c>
-      <c r="H30" s="1" t="inlineStr"/>
-      <c r="I30" s="1" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr"/>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="H31" s="1" t="inlineStr"/>
+      <c r="I31" s="1" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr"/>
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>3. Канализация ливневая К2. Сборный колодец КЛ-1</t>
         </is>
       </c>
-      <c r="C31" s="1" t="n"/>
-      <c r="D31" s="1" t="n"/>
-      <c r="E31" s="1" t="n"/>
-      <c r="F31" s="1" t="n"/>
-      <c r="G31" s="1" t="n"/>
-      <c r="H31" s="1" t="n"/>
-      <c r="I31" s="1" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Труба ПП гофрированная двухслойная SN8 Ø110 с раструбом и уплотнительным кольцом</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>ГОСТ 32413-2013</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="inlineStr"/>
-      <c r="E32" s="1" t="inlineStr"/>
-      <c r="F32" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G32" s="1" t="n">
-        <v>165</v>
-      </c>
-      <c r="H32" s="1" t="inlineStr"/>
-      <c r="I32" s="1" t="inlineStr">
-        <is>
-          <t>кольца К2 дома и бани, транзит, выпуск лотка гаража</t>
-        </is>
-      </c>
+      <c r="C32" s="1" t="n"/>
+      <c r="D32" s="1" t="n"/>
+      <c r="E32" s="1" t="n"/>
+      <c r="F32" s="1" t="n"/>
+      <c r="G32" s="1" t="n"/>
+      <c r="H32" s="1" t="n"/>
+      <c r="I32" s="1" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Труба напорная ПЭ 100 SDR17 63×3,8</t>
+          <t>Труба ПП гофрированная двухслойная SN8 Ø110 с раструбом и уплотнительным кольцом</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 18599-2001</t>
+          <t>ГОСТ 32413-2013</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr"/>
@@ -1392,12 +1392,12 @@
         </is>
       </c>
       <c r="G33" s="1" t="n">
-        <v>2</v>
+        <v>165</v>
       </c>
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr">
         <is>
-          <t>выпуск КЛ-1 → выпуск ЛК Ø63</t>
+          <t>кольца К2 дома и бани, транзит, выпуск лотка гаража</t>
         </is>
       </c>
     </row>
@@ -1407,28 +1407,28 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Муфта электросварная ПЭ 100 Ø63</t>
+          <t>Труба напорная ПЭ 100 SDR17 63×3,8</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 18599-2001</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr"/>
       <c r="E34" s="1" t="inlineStr"/>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G34" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>стык с выпуском ЛК (после шурфа)</t>
+          <t>выпуск КЛ-1 → выпуск ЛК Ø63</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП Ø110, 45°</t>
+          <t>Муфта электросварная ПЭ 100 Ø63</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
@@ -1454,12 +1454,12 @@
         </is>
       </c>
       <c r="G35" s="1" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>углы колец и вводов в КЛ-1 (по 2 на угол), транзит, выпуск гаража; выпуски водостоков — по 2</t>
+          <t>стык с выпуском ЛК (после шурфа)</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП Ø110, 90°</t>
+          <t>Отвод ПП Ø110, 45°</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
@@ -1485,12 +1485,12 @@
         </is>
       </c>
       <c r="G36" s="1" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>слияние полуколец бани, приём транзита бани</t>
+          <t>углы колец и вводов в КЛ-1 (по 2 на угол), транзит, выпуск гаража; выпуски водостоков — по 2</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП Ø110 косой 45°</t>
+          <t>Тройник ПП Ø110, 90°</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
@@ -1516,12 +1516,12 @@
         </is>
       </c>
       <c r="G37" s="1" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>выпуски водостоков (8, ориентировочно — по привязке воронок) и лотка гаража</t>
+          <t>слияние полуколец бани, приём транзита бани</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Футляр (гильза) из трубы ПП Ø160, L = 0,6 м — закладная в край плиты</t>
+          <t>Тройник ПП Ø110 косой 45°</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
@@ -1547,12 +1547,12 @@
         </is>
       </c>
       <c r="G38" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr">
         <is>
-          <t>выпуски водостоков (узел 9), ориентировочно; закладка — при бетонировании (КР)</t>
+          <t>выпуски водостоков (8, ориентировочно — по привязке воронок) и лотка гаража</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Плита днища ПН15</t>
+          <t>Футляр (гильза) из трубы ПП Ø160, L = 0,6 м — закладная в край плиты</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 8020-2016</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr"/>
@@ -1578,12 +1578,12 @@
         </is>
       </c>
       <c r="G39" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1 (лист 8, узел 2)</t>
+          <t>выпуски водостоков (узел 9), ориентировочно; закладка — при бетонировании (КР)</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Кольцо стеновое КС15.9</t>
+          <t>Плита днища ПН15</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
@@ -1614,7 +1614,7 @@
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1</t>
+          <t>КЛ-1 (лист 8, узел 2)</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Кольцо стеновое КС15.6</t>
+          <t>Кольцо стеновое КС15.9</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Плита перекрытия 1ПП15-1</t>
+          <t>Кольцо стеновое КС15.6</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Кольцо стеновое КС7.3 (горловина)</t>
+          <t>Плита перекрытия 1ПП15-1</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Люк чугунный тяжёлый Т (C250)</t>
+          <t>Кольцо стеновое КС7.3 (горловина)</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 3634-2019</t>
+          <t>ГОСТ 8020-2016</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr"/>
@@ -1738,7 +1738,7 @@
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1 — в зоне заезда</t>
+          <t>КЛ-1</t>
         </is>
       </c>
     </row>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Скобы ходовые</t>
+          <t>Люк чугунный тяжёлый Т (C250)</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 8020-2016</t>
+          <t>ГОСТ 3634-2019</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr"/>
@@ -1764,12 +1764,12 @@
         </is>
       </c>
       <c r="G45" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1, шаг 0,3 м</t>
+          <t>КЛ-1 — в зоне заезда</t>
         </is>
       </c>
     </row>
@@ -1779,28 +1779,28 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Мастика битумная для наружной гидроизоляции колец, 2 слоя</t>
+          <t>Скобы ходовые</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 8020-2016</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr"/>
       <c r="E46" s="1" t="inlineStr"/>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G46" s="1" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1, наружная поверхность</t>
+          <t>КЛ-1, шаг 0,3 м</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø110</t>
+          <t>Мастика битумная для наружной гидроизоляции колец, 2 слоя</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
@@ -1822,16 +1822,16 @@
       <c r="E47" s="1" t="inlineStr"/>
       <c r="F47" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G47" s="1" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1: К2-К, К2-Б, Др-К</t>
+          <t>КЛ-1, наружная поверхность</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø63</t>
+          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø110</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
@@ -1857,12 +1857,12 @@
         </is>
       </c>
       <c r="G48" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1: выпуск</t>
+          <t>КЛ-1: К2-К, К2-Б, Др-К</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный канализационный (захлопка) Ø110</t>
+          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø63</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
@@ -1893,7 +1893,7 @@
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1: вход дренажа Др-К</t>
+          <t>КЛ-1: выпуск</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Решётка-корзина из нержавеющей стали на входе выпуска Ø63</t>
+          <t>Клапан обратный канализационный (захлопка) Ø110</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
@@ -1924,55 +1924,55 @@
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr">
         <is>
+          <t>КЛ-1: вход дренажа Др-К</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Решётка-корзина из нержавеющей стали на входе выпуска Ø63</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="inlineStr"/>
+      <c r="E51" s="1" t="inlineStr"/>
+      <c r="F51" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="1" t="inlineStr"/>
+      <c r="I51" s="1" t="inlineStr">
+        <is>
           <t>КЛ-1</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr"/>
-      <c r="B51" s="3" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr"/>
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>4. Дренаж Др</t>
         </is>
       </c>
-      <c r="C51" s="1" t="n"/>
-      <c r="D51" s="1" t="n"/>
-      <c r="E51" s="1" t="n"/>
-      <c r="F51" s="1" t="n"/>
-      <c r="G51" s="1" t="n"/>
-      <c r="H51" s="1" t="n"/>
-      <c r="I51" s="1" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>46</v>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Труба дренажная гофрированная перфорированная Ø110 в фильтре из геотекстиля</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>ГОСТ Р 59249-2020 или ТУ изготовителя</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr"/>
-      <c r="E52" s="1" t="inlineStr"/>
-      <c r="F52" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G52" s="1" t="n">
-        <v>150</v>
-      </c>
-      <c r="H52" s="1" t="inlineStr"/>
-      <c r="I52" s="1" t="inlineStr">
-        <is>
-          <t>кольца дренажа дома и бани</t>
-        </is>
-      </c>
+      <c r="C52" s="1" t="n"/>
+      <c r="D52" s="1" t="n"/>
+      <c r="E52" s="1" t="n"/>
+      <c r="F52" s="1" t="n"/>
+      <c r="G52" s="1" t="n"/>
+      <c r="H52" s="1" t="n"/>
+      <c r="I52" s="1" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Труба ПП гофрированная двухслойная SN8 Ø110 (без перфорации)</t>
+          <t>Труба дренажная гофрированная перфорированная Ø110 в фильтре из геотекстиля</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32413-2013</t>
+          <t>ГОСТ Р 59249-2020 или ТУ изготовителя</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr"/>
@@ -1996,12 +1996,12 @@
         </is>
       </c>
       <c r="G53" s="1" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr">
         <is>
-          <t>транзит Др-Т, выход Др-К в КЛ-1</t>
+          <t>кольца дренажа дома и бани</t>
         </is>
       </c>
     </row>
@@ -2011,28 +2011,28 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Колодец дренажный полимерный: шахта гофр. Ø315, днище, крышка</t>
+          <t>Труба ПП гофрированная двухслойная SN8 Ø110 (без перфорации)</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32413-2013</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr"/>
       <c r="E54" s="1" t="inlineStr"/>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G54" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr">
         <is>
-          <t>Др-1…Др-4, ДрБ-1…ДрБ-4 (лист 8, узел 5)</t>
+          <t>транзит Др-Т, выход Др-К в КЛ-1</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная Ø315 для шахт дренажных колодцев</t>
+          <t>Колодец дренажный полимерный: шахта гофр. Ø315, днище, крышка</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -2054,16 +2054,16 @@
       <c r="E55" s="1" t="inlineStr"/>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G55" s="1" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr">
         <is>
-          <t>H = 1,54…1,79 м, отстойная часть 0,3 м</t>
+          <t>Др-1…Др-4, ДрБ-1…ДрБ-4 (лист 8, узел 5)</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Уплотнитель резиновый для ввода трубы Ø110 в колодец Ø315</t>
+          <t>Труба гофрированная Ø315 для шахт дренажных колодцев</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -2085,14 +2085,18 @@
       <c r="E56" s="1" t="inlineStr"/>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G56" s="1" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H56" s="1" t="inlineStr"/>
-      <c r="I56" s="1" t="inlineStr"/>
+      <c r="I56" s="1" t="inlineStr">
+        <is>
+          <t>H = 1,54…1,79 м, отстойная часть 0,3 м</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -2100,12 +2104,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Люк чугунный тяжёлый Т (C250) с опорным кольцом для колодца Ø315</t>
+          <t>Уплотнитель резиновый для ввода трубы Ø110 в колодец Ø315</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 3634-2019</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr"/>
@@ -2116,60 +2120,56 @@
         </is>
       </c>
       <c r="G57" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="H57" s="1" t="inlineStr"/>
+      <c r="I57" s="1" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Люк чугунный тяжёлый Т (C250) с опорным кольцом для колодца Ø315</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>ГОСТ 3634-2019</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="inlineStr"/>
+      <c r="E58" s="1" t="inlineStr"/>
+      <c r="F58" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G58" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="H57" s="1" t="inlineStr"/>
-      <c r="I57" s="1" t="inlineStr">
+      <c r="H58" s="1" t="inlineStr"/>
+      <c r="I58" s="1" t="inlineStr">
         <is>
           <t>Др-1, Др-3, ДрБ-2, ДрБ-3 — в зоне заезда</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr"/>
-      <c r="B58" s="3" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr"/>
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>5. Материалы траншей и утепление</t>
         </is>
       </c>
-      <c r="C58" s="1" t="n"/>
-      <c r="D58" s="1" t="n"/>
-      <c r="E58" s="1" t="n"/>
-      <c r="F58" s="1" t="n"/>
-      <c r="G58" s="1" t="n"/>
-      <c r="H58" s="1" t="n"/>
-      <c r="I58" s="1" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Песок средней крупности для основания и обсыпки труб и колодцев, засыпки в зоне заезда</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>ГОСТ 8736-2014</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr"/>
-      <c r="E59" s="1" t="inlineStr"/>
-      <c r="F59" s="1" t="inlineStr">
-        <is>
-          <t>м³</t>
-        </is>
-      </c>
-      <c r="G59" s="1" t="n">
-        <v>155.5</v>
-      </c>
-      <c r="H59" s="1" t="inlineStr"/>
-      <c r="I59" s="1" t="inlineStr">
-        <is>
-          <t>основание 100 мм, обсыпка 300 мм; в зоне заезда — на всю глубину (77,4 м³)</t>
-        </is>
-      </c>
+      <c r="C59" s="1" t="n"/>
+      <c r="D59" s="1" t="n"/>
+      <c r="E59" s="1" t="n"/>
+      <c r="F59" s="1" t="n"/>
+      <c r="G59" s="1" t="n"/>
+      <c r="H59" s="1" t="n"/>
+      <c r="I59" s="1" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Щебень гранитный фракции 20–40 мм, промытый</t>
+          <t>Песок средней крупности для основания и обсыпки труб и колодцев, засыпки в зоне заезда</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 8267-93</t>
+          <t>ГОСТ 8736-2014</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr"/>
@@ -2193,12 +2193,12 @@
         </is>
       </c>
       <c r="G60" s="1" t="n">
-        <v>33</v>
+        <v>155</v>
       </c>
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr">
         <is>
-          <t>призма вокруг дренажа (узел 8), основание КЛ-1</t>
+          <t>основание 100 мм, обсыпка 300 мм; в зоне заезда — на всю глубину (76,7 м³)</t>
         </is>
       </c>
     </row>
@@ -2208,28 +2208,28 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Геотекстиль иглопробивной 150–200 г/м²</t>
+          <t>Щебень гранитный фракции 20–40 мм, промытый</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 8267-93</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr"/>
       <c r="E61" s="1" t="inlineStr"/>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>м³</t>
         </is>
       </c>
       <c r="G61" s="1" t="n">
-        <v>360</v>
+        <v>33</v>
       </c>
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr">
         <is>
-          <t>обёртка щебня, нахлёст 0,3 м</t>
+          <t>призма вокруг дренажа (узел 8), основание КЛ-1</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Плиты ЭППС 50 мм, плотность не менее 35 кг/м³</t>
+          <t>Геотекстиль иглопробивной 150–200 г/м²</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
@@ -2255,46 +2255,60 @@
         </is>
       </c>
       <c r="G62" s="1" t="n">
-        <v>2</v>
+        <v>360</v>
       </c>
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr">
         <is>
+          <t>обёртка щебня, нахлёст 0,3 м</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Плиты ЭППС 50 мм, плотность не менее 35 кг/м³</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="inlineStr"/>
+      <c r="E63" s="1" t="inlineStr"/>
+      <c r="F63" s="1" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="G63" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H63" s="1" t="inlineStr"/>
+      <c r="I63" s="1" t="inlineStr">
+        <is>
           <t>полоса 1,2 м над трубой на мелких участках (узел 6)</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="1" t="inlineStr"/>
-      <c r="B63" s="3" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr"/>
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>6. Не входит в НВК.СО</t>
         </is>
       </c>
-      <c r="C63" s="1" t="n"/>
-      <c r="D63" s="1" t="n"/>
-      <c r="E63" s="1" t="n"/>
-      <c r="F63" s="1" t="n"/>
-      <c r="G63" s="1" t="n"/>
-      <c r="H63" s="1" t="n"/>
-      <c r="I63" s="1" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="n">
-        <v>56</v>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Стояки внутренних водостоков в стенах, выпуски К1, ввод В1 и подводка КХ-8 до наружной грани фундамента, лоток гаража ЛГ-1 с пескоуловителем — И05.09.26-ВК.СО</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr"/>
-      <c r="D64" s="1" t="inlineStr"/>
-      <c r="E64" s="1" t="inlineStr"/>
-      <c r="F64" s="1" t="inlineStr"/>
-      <c r="G64" s="1" t="inlineStr"/>
-      <c r="H64" s="1" t="inlineStr"/>
-      <c r="I64" s="1" t="inlineStr"/>
+      <c r="C64" s="1" t="n"/>
+      <c r="D64" s="1" t="n"/>
+      <c r="E64" s="1" t="n"/>
+      <c r="F64" s="1" t="n"/>
+      <c r="G64" s="1" t="n"/>
+      <c r="H64" s="1" t="n"/>
+      <c r="I64" s="1" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -2302,7 +2316,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Утеплённая отмостка, утепление торца плиты, футляры в фундаменте — КР/АР</t>
+          <t>Стояки внутренних водостоков в стенах, выпуски К1, ввод В1 и подводка КХ-8 до наружной грани фундамента, лоток гаража ЛГ-1 с пескоуловителем — И05.09.26-ВК.СО</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr"/>
@@ -2319,7 +2333,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Терморегулятор и питание греющего кабеля — ЭОМ</t>
+          <t>Утеплённая отмостка, утепление торца плиты, футляры в фундаменте — КР/АР</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr"/>
@@ -2336,7 +2350,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Автополив участка от КП-1 — по ландшафтному проекту</t>
+          <t>Терморегулятор и питание греющего кабеля — ЭОМ</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr"/>
@@ -2347,9 +2361,26 @@
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr"/>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Автополив участка от КП-1 — по ландшафтному проекту</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="inlineStr"/>
+      <c r="D68" s="1" t="inlineStr"/>
+      <c r="E68" s="1" t="inlineStr"/>
+      <c r="F68" s="1" t="inlineStr"/>
+      <c r="G68" s="1" t="inlineStr"/>
+      <c r="H68" s="1" t="inlineStr"/>
+      <c r="I68" s="1" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
         <is>
           <t>Примечание — Допускается применение оборудования, изделий и материалов других изготовителей с техническими характеристиками не ниже указанных в настоящей спецификации.</t>
         </is>

--- a/ovk-dom-banya/release-nvk/И05.09.26-НВК.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-nvk/И05.09.26-НВК.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1102,12 +1102,12 @@
         </is>
       </c>
       <c r="G23" s="1" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr">
         <is>
-          <t>выпуски К1-1н, К1-бн</t>
+          <t>выпуск К1-1н, линия бани К1-бн, К1-б1 (прямые, без поворотов)</t>
         </is>
       </c>
     </row>
@@ -1117,28 +1117,28 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Труба ПП гофрированная двухслойная SN8 Ø160 с раструбом и уплотнительным кольцом</t>
+          <t>Колодец канализационный полимерный Ø630 с проточным лотком (проход Ø110, перепад 0,02 м), шахтой гофр. Ø400 телескопической, H = 0,87 м, люк Л</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32413-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr"/>
       <c r="E24" s="1" t="inlineStr"/>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G24" s="1" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="H24" s="1" t="inlineStr"/>
       <c r="I24" s="1" t="inlineStr">
         <is>
-          <t>сеть бани К1-б1…К1-б3</t>
+          <t>КК-1 (лист 8, узел 4)</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП Ø110, 15°</t>
+          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø110</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
@@ -1169,7 +1169,7 @@
       <c r="H25" s="1" t="inlineStr"/>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>стык с выпуском К1-1 (ВК), угол — по месту</t>
+          <t>врезка К1-1н в ДК5-018 (узел 3)</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Колодец канализационный полимерный Ø630 с проточным лотком (приём Ø110, выход Ø160), шахтой гофр. Ø400 телескопической, H = 0,96 м, люк Л</t>
+          <t>Лента сигнальная «Осторожно! Канализация»</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
@@ -1191,119 +1191,99 @@
       <c r="E26" s="1" t="inlineStr"/>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G26" s="1" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H26" s="1" t="inlineStr"/>
-      <c r="I26" s="1" t="inlineStr">
-        <is>
-          <t>КК-1 (лист 8, узел 4)</t>
-        </is>
-      </c>
+      <c r="I26" s="1" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Колодец канализационный полимерный Ø630 с проточным лотком (проход Ø160, поворот 90°), шахтой гофр. Ø400 телескопической, H = 1,19 м, люк Т (C250) на опорном кольце — зона заезда</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr"/>
-      <c r="E27" s="1" t="inlineStr"/>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G27" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="1" t="inlineStr"/>
-      <c r="I27" s="1" t="inlineStr">
-        <is>
-          <t>КК-2 (лист 8, узел 4)</t>
-        </is>
-      </c>
+      <c r="A27" s="1" t="inlineStr"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>3. Канализация ливневая К2. Сборный колодец КЛ-1</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="n"/>
+      <c r="D27" s="1" t="n"/>
+      <c r="E27" s="1" t="n"/>
+      <c r="F27" s="1" t="n"/>
+      <c r="G27" s="1" t="n"/>
+      <c r="H27" s="1" t="n"/>
+      <c r="I27" s="1" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Колодец канализационный полимерный Ø630 с проточным лотком (проход Ø160, поворот 81°), шахтой гофр. Ø400 телескопической, H = 1,44 м, люк Т (C250) на опорном кольце — зона заезда</t>
+          <t>Труба ПП гофрированная двухслойная SN8 Ø110 с раструбом и уплотнительным кольцом</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32413-2013</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr"/>
       <c r="E28" s="1" t="inlineStr"/>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G28" s="1" t="n">
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>КК-3 (лист 8, узел 4)</t>
+          <t>кольца К2 дома и бани, транзит, выпуск лотка гаража</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø110</t>
+          <t>Труба напорная ПЭ 100 SDR17 63×3,8</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 18599-2001</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr"/>
       <c r="E29" s="1" t="inlineStr"/>
       <c r="F29" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G29" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr">
         <is>
-          <t>врезка К1-1н в ДК5-018 (узел 3)</t>
+          <t>выпуск КЛ-1 → выпуск ЛК Ø63</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø160</t>
+          <t>Муфта электросварная ПЭ 100 Ø63</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
@@ -1324,17 +1304,17 @@
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr">
         <is>
-          <t>врезка К1-б3 в ДК5-018 (узел 3)</t>
+          <t>стык с выпуском ЛК (после шурфа)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Лента сигнальная «Осторожно! Канализация»</t>
+          <t>Отвод ПП Ø110, 45°</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
@@ -1346,29 +1326,49 @@
       <c r="E31" s="1" t="inlineStr"/>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G31" s="1" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="H31" s="1" t="inlineStr"/>
-      <c r="I31" s="1" t="inlineStr"/>
+      <c r="I31" s="1" t="inlineStr">
+        <is>
+          <t>углы колец и вводов в КЛ-1 (по 2 на угол), транзит, выпуск гаража; выпуски водостоков — по 2</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr"/>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>3. Канализация ливневая К2. Сборный колодец КЛ-1</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="n"/>
-      <c r="D32" s="1" t="n"/>
-      <c r="E32" s="1" t="n"/>
-      <c r="F32" s="1" t="n"/>
-      <c r="G32" s="1" t="n"/>
-      <c r="H32" s="1" t="n"/>
-      <c r="I32" s="1" t="n"/>
+      <c r="A32" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Тройник ПП Ø110, 90°</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr"/>
+      <c r="E32" s="1" t="inlineStr"/>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="1" t="inlineStr"/>
+      <c r="I32" s="1" t="inlineStr">
+        <is>
+          <t>слияние полуколец бани, приём транзита бани</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -1376,28 +1376,28 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Труба ПП гофрированная двухслойная SN8 Ø110 с раструбом и уплотнительным кольцом</t>
+          <t>Тройник ПП Ø110 косой 45°</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32413-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr"/>
       <c r="E33" s="1" t="inlineStr"/>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G33" s="1" t="n">
-        <v>165</v>
+        <v>9</v>
       </c>
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr">
         <is>
-          <t>кольца К2 дома и бани, транзит, выпуск лотка гаража</t>
+          <t>выпуски водостоков (8, ориентировочно — по привязке воронок) и лотка гаража</t>
         </is>
       </c>
     </row>
@@ -1407,28 +1407,28 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Труба напорная ПЭ 100 SDR17 63×3,8</t>
+          <t>Футляр (гильза) из трубы ПП Ø160, L = 0,6 м — закладная в край плиты</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 18599-2001</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr"/>
       <c r="E34" s="1" t="inlineStr"/>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G34" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>выпуск КЛ-1 → выпуск ЛК Ø63</t>
+          <t>выпуски водостоков (узел 9), ориентировочно; закладка — при бетонировании (КР)</t>
         </is>
       </c>
     </row>
@@ -1438,12 +1438,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Муфта электросварная ПЭ 100 Ø63</t>
+          <t>Плита днища ПН15</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 8020-2016</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr"/>
@@ -1459,7 +1459,7 @@
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>стык с выпуском ЛК (после шурфа)</t>
+          <t>КЛ-1 (лист 8, узел 2)</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП Ø110, 45°</t>
+          <t>Кольцо стеновое КС15.9</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 8020-2016</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr"/>
@@ -1485,12 +1485,12 @@
         </is>
       </c>
       <c r="G36" s="1" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>углы колец и вводов в КЛ-1 (по 2 на угол), транзит, выпуск гаража; выпуски водостоков — по 2</t>
+          <t>КЛ-1</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП Ø110, 90°</t>
+          <t>Кольцо стеновое КС15.6</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 8020-2016</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr"/>
@@ -1516,12 +1516,12 @@
         </is>
       </c>
       <c r="G37" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>слияние полуколец бани, приём транзита бани</t>
+          <t>КЛ-1</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП Ø110 косой 45°</t>
+          <t>Плита перекрытия 1ПП15-1</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 8020-2016</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr"/>
@@ -1547,12 +1547,12 @@
         </is>
       </c>
       <c r="G38" s="1" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr">
         <is>
-          <t>выпуски водостоков (8, ориентировочно — по привязке воронок) и лотка гаража</t>
+          <t>КЛ-1</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Футляр (гильза) из трубы ПП Ø160, L = 0,6 м — закладная в край плиты</t>
+          <t>Кольцо стеновое КС7.3 (горловина)</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 8020-2016</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr"/>
@@ -1578,12 +1578,12 @@
         </is>
       </c>
       <c r="G39" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>выпуски водостоков (узел 9), ориентировочно; закладка — при бетонировании (КР)</t>
+          <t>КЛ-1</t>
         </is>
       </c>
     </row>
@@ -1593,12 +1593,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Плита днища ПН15</t>
+          <t>Люк чугунный тяжёлый Т (C250)</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 8020-2016</t>
+          <t>ГОСТ 3634-2019</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr"/>
@@ -1614,7 +1614,7 @@
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1 (лист 8, узел 2)</t>
+          <t>КЛ-1 — в зоне заезда</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Кольцо стеновое КС15.9</t>
+          <t>Скобы ходовые</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -1640,12 +1640,12 @@
         </is>
       </c>
       <c r="G41" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1</t>
+          <t>КЛ-1, шаг 0,3 м</t>
         </is>
       </c>
     </row>
@@ -1655,28 +1655,28 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Кольцо стеновое КС15.6</t>
+          <t>Мастика битумная для наружной гидроизоляции колец, 2 слоя</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 8020-2016</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr"/>
       <c r="E42" s="1" t="inlineStr"/>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G42" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1</t>
+          <t>КЛ-1, наружная поверхность</t>
         </is>
       </c>
     </row>
@@ -1686,12 +1686,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Плита перекрытия 1ПП15-1</t>
+          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø110</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 8020-2016</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr"/>
@@ -1702,12 +1702,12 @@
         </is>
       </c>
       <c r="G43" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1</t>
+          <t>КЛ-1: К2-К, К2-Б, Др-К</t>
         </is>
       </c>
     </row>
@@ -1717,12 +1717,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Кольцо стеновое КС7.3 (горловина)</t>
+          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø63</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 8020-2016</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr"/>
@@ -1738,7 +1738,7 @@
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1</t>
+          <t>КЛ-1: выпуск</t>
         </is>
       </c>
     </row>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Люк чугунный тяжёлый Т (C250)</t>
+          <t>Клапан обратный канализационный (захлопка) Ø110</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 3634-2019</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr"/>
@@ -1769,7 +1769,7 @@
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1 — в зоне заезда</t>
+          <t>КЛ-1: вход дренажа Др-К</t>
         </is>
       </c>
     </row>
@@ -1779,12 +1779,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Скобы ходовые</t>
+          <t>Решётка-корзина из нержавеющей стали на входе выпуска Ø63</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 8020-2016</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr"/>
@@ -1795,115 +1795,99 @@
         </is>
       </c>
       <c r="G46" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1, шаг 0,3 м</t>
+          <t>КЛ-1</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Мастика битумная для наружной гидроизоляции колец, 2 слоя</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr"/>
-      <c r="E47" s="1" t="inlineStr"/>
-      <c r="F47" s="1" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="G47" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="H47" s="1" t="inlineStr"/>
-      <c r="I47" s="1" t="inlineStr">
-        <is>
-          <t>КЛ-1, наружная поверхность</t>
-        </is>
-      </c>
+      <c r="A47" s="1" t="inlineStr"/>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>4. Дренаж Др</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="n"/>
+      <c r="D47" s="1" t="n"/>
+      <c r="E47" s="1" t="n"/>
+      <c r="F47" s="1" t="n"/>
+      <c r="G47" s="1" t="n"/>
+      <c r="H47" s="1" t="n"/>
+      <c r="I47" s="1" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø110</t>
+          <t>Труба дренажная гофрированная перфорированная Ø110 в фильтре из геотекстиля</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ Р 59249-2020 или ТУ изготовителя</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr"/>
       <c r="E48" s="1" t="inlineStr"/>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G48" s="1" t="n">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1: К2-К, К2-Б, Др-К</t>
+          <t>кольца дренажа дома и бани</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø63</t>
+          <t>Труба ПП гофрированная двухслойная SN8 Ø110 (без перфорации)</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32413-2013</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr"/>
       <c r="E49" s="1" t="inlineStr"/>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G49" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1: выпуск</t>
+          <t>транзит Др-Т, выход Др-К в КЛ-1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный канализационный (захлопка) Ø110</t>
+          <t>Колодец дренажный полимерный: шахта гофр. Ø315, днище, крышка</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
@@ -1919,22 +1903,22 @@
         </is>
       </c>
       <c r="G50" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1: вход дренажа Др-К</t>
+          <t>Др-1…Др-4, ДрБ-1…ДрБ-4 (лист 8, узел 5)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Решётка-корзина из нержавеющей стали на входе выпуска Ø63</t>
+          <t>Труба гофрированная Ø315 для шахт дренажных колодцев</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
@@ -1946,33 +1930,45 @@
       <c r="E51" s="1" t="inlineStr"/>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G51" s="1" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1</t>
+          <t>H = 1,54…1,79 м, отстойная часть 0,3 м</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="inlineStr"/>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>4. Дренаж Др</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="n"/>
-      <c r="D52" s="1" t="n"/>
-      <c r="E52" s="1" t="n"/>
-      <c r="F52" s="1" t="n"/>
-      <c r="G52" s="1" t="n"/>
-      <c r="H52" s="1" t="n"/>
-      <c r="I52" s="1" t="n"/>
+      <c r="A52" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Уплотнитель резиновый для ввода трубы Ø110 в колодец Ø315</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="inlineStr"/>
+      <c r="E52" s="1" t="inlineStr"/>
+      <c r="F52" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G52" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="H52" s="1" t="inlineStr"/>
+      <c r="I52" s="1" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -1980,131 +1976,115 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Труба дренажная гофрированная перфорированная Ø110 в фильтре из геотекстиля</t>
+          <t>Люк чугунный тяжёлый Т (C250) с опорным кольцом для колодца Ø315</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ Р 59249-2020 или ТУ изготовителя</t>
+          <t>ГОСТ 3634-2019</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr"/>
       <c r="E53" s="1" t="inlineStr"/>
       <c r="F53" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G53" s="1" t="n">
-        <v>150</v>
+        <v>4</v>
       </c>
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr">
         <is>
-          <t>кольца дренажа дома и бани</t>
+          <t>Др-1, Др-3, ДрБ-2, ДрБ-3 — в зоне заезда</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Труба ПП гофрированная двухслойная SN8 Ø110 (без перфорации)</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>ГОСТ 32413-2013</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr"/>
-      <c r="E54" s="1" t="inlineStr"/>
-      <c r="F54" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G54" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="H54" s="1" t="inlineStr"/>
-      <c r="I54" s="1" t="inlineStr">
-        <is>
-          <t>транзит Др-Т, выход Др-К в КЛ-1</t>
-        </is>
-      </c>
+      <c r="A54" s="1" t="inlineStr"/>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>5. Материалы траншей и утепление</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="n"/>
+      <c r="D54" s="1" t="n"/>
+      <c r="E54" s="1" t="n"/>
+      <c r="F54" s="1" t="n"/>
+      <c r="G54" s="1" t="n"/>
+      <c r="H54" s="1" t="n"/>
+      <c r="I54" s="1" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Колодец дренажный полимерный: шахта гофр. Ø315, днище, крышка</t>
+          <t>Песок средней крупности для основания и обсыпки труб и колодцев, засыпки в зоне заезда</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 8736-2014</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr"/>
       <c r="E55" s="1" t="inlineStr"/>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м³</t>
         </is>
       </c>
       <c r="G55" s="1" t="n">
-        <v>8</v>
+        <v>113</v>
       </c>
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr">
         <is>
-          <t>Др-1…Др-4, ДрБ-1…ДрБ-4 (лист 8, узел 5)</t>
+          <t>основание 100 мм, обсыпка 300 мм; в зоне заезда — на всю глубину (58,3 м³)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная Ø315 для шахт дренажных колодцев</t>
+          <t>Щебень гранитный фракции 20–40 мм, промытый</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 8267-93</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr"/>
       <c r="E56" s="1" t="inlineStr"/>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>м³</t>
         </is>
       </c>
       <c r="G56" s="1" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr">
         <is>
-          <t>H = 1,54…1,79 м, отстойная часть 0,3 м</t>
+          <t>призма вокруг дренажа (узел 8), основание КЛ-1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Уплотнитель резиновый для ввода трубы Ø110 в колодец Ø315</t>
+          <t>Геотекстиль иглопробивной 150–200 г/м²</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -2116,34 +2096,38 @@
       <c r="E57" s="1" t="inlineStr"/>
       <c r="F57" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G57" s="1" t="n">
-        <v>19</v>
+        <v>360</v>
       </c>
       <c r="H57" s="1" t="inlineStr"/>
-      <c r="I57" s="1" t="inlineStr"/>
+      <c r="I57" s="1" t="inlineStr">
+        <is>
+          <t>обёртка щебня, нахлёст 0,3 м</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Люк чугунный тяжёлый Т (C250) с опорным кольцом для колодца Ø315</t>
+          <t>Плиты ЭППС 50 мм, плотность не менее 35 кг/м³</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 3634-2019</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr"/>
       <c r="E58" s="1" t="inlineStr"/>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G58" s="1" t="n">
@@ -2152,7 +2136,7 @@
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>Др-1, Др-3, ДрБ-2, ДрБ-3 — в зоне заезда</t>
+          <t>полоса 1,2 м над трубой на мелких участках (узел 6)</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2144,7 @@
       <c r="A59" s="1" t="inlineStr"/>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>5. Материалы траншей и утепление</t>
+          <t>6. Не входит в НВК.СО</t>
         </is>
       </c>
       <c r="C59" s="1" t="n"/>
@@ -2173,214 +2157,75 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Песок средней крупности для основания и обсыпки труб и колодцев, засыпки в зоне заезда</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>ГОСТ 8736-2014</t>
-        </is>
-      </c>
+          <t>Стояки внутренних водостоков в стенах, выпуски К1, ввод В1 и подводка КХ-8 до наружной грани фундамента, лоток гаража ЛГ-1 с пескоуловителем — И05.09.26-ВК.СО</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="inlineStr"/>
       <c r="D60" s="1" t="inlineStr"/>
       <c r="E60" s="1" t="inlineStr"/>
-      <c r="F60" s="1" t="inlineStr">
-        <is>
-          <t>м³</t>
-        </is>
-      </c>
-      <c r="G60" s="1" t="n">
-        <v>155</v>
-      </c>
+      <c r="F60" s="1" t="inlineStr"/>
+      <c r="G60" s="1" t="inlineStr"/>
       <c r="H60" s="1" t="inlineStr"/>
-      <c r="I60" s="1" t="inlineStr">
-        <is>
-          <t>основание 100 мм, обсыпка 300 мм; в зоне заезда — на всю глубину (76,7 м³)</t>
-        </is>
-      </c>
+      <c r="I60" s="1" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Щебень гранитный фракции 20–40 мм, промытый</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>ГОСТ 8267-93</t>
-        </is>
-      </c>
+          <t>Утеплённая отмостка, утепление торца плиты, футляры в фундаменте — КР/АР</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="inlineStr"/>
       <c r="D61" s="1" t="inlineStr"/>
       <c r="E61" s="1" t="inlineStr"/>
-      <c r="F61" s="1" t="inlineStr">
-        <is>
-          <t>м³</t>
-        </is>
-      </c>
-      <c r="G61" s="1" t="n">
-        <v>33</v>
-      </c>
+      <c r="F61" s="1" t="inlineStr"/>
+      <c r="G61" s="1" t="inlineStr"/>
       <c r="H61" s="1" t="inlineStr"/>
-      <c r="I61" s="1" t="inlineStr">
-        <is>
-          <t>призма вокруг дренажа (узел 8), основание КЛ-1</t>
-        </is>
-      </c>
+      <c r="I61" s="1" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Геотекстиль иглопробивной 150–200 г/м²</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Терморегулятор и питание греющего кабеля — ЭОМ</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="inlineStr"/>
       <c r="D62" s="1" t="inlineStr"/>
       <c r="E62" s="1" t="inlineStr"/>
-      <c r="F62" s="1" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="G62" s="1" t="n">
-        <v>360</v>
-      </c>
+      <c r="F62" s="1" t="inlineStr"/>
+      <c r="G62" s="1" t="inlineStr"/>
       <c r="H62" s="1" t="inlineStr"/>
-      <c r="I62" s="1" t="inlineStr">
-        <is>
-          <t>обёртка щебня, нахлёст 0,3 м</t>
-        </is>
-      </c>
+      <c r="I62" s="1" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Плиты ЭППС 50 мм, плотность не менее 35 кг/м³</t>
-        </is>
-      </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Автополив участка от КП-1 — по ландшафтному проекту</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr"/>
       <c r="D63" s="1" t="inlineStr"/>
       <c r="E63" s="1" t="inlineStr"/>
-      <c r="F63" s="1" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="G63" s="1" t="n">
-        <v>2</v>
-      </c>
+      <c r="F63" s="1" t="inlineStr"/>
+      <c r="G63" s="1" t="inlineStr"/>
       <c r="H63" s="1" t="inlineStr"/>
-      <c r="I63" s="1" t="inlineStr">
-        <is>
-          <t>полоса 1,2 м над трубой на мелких участках (узел 6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr"/>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>6. Не входит в НВК.СО</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="n"/>
-      <c r="D64" s="1" t="n"/>
-      <c r="E64" s="1" t="n"/>
-      <c r="F64" s="1" t="n"/>
-      <c r="G64" s="1" t="n"/>
-      <c r="H64" s="1" t="n"/>
-      <c r="I64" s="1" t="n"/>
+      <c r="I63" s="1" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
-        <v>57</v>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Стояки внутренних водостоков в стенах, выпуски К1, ввод В1 и подводка КХ-8 до наружной грани фундамента, лоток гаража ЛГ-1 с пескоуловителем — И05.09.26-ВК.СО</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr"/>
-      <c r="D65" s="1" t="inlineStr"/>
-      <c r="E65" s="1" t="inlineStr"/>
-      <c r="F65" s="1" t="inlineStr"/>
-      <c r="G65" s="1" t="inlineStr"/>
-      <c r="H65" s="1" t="inlineStr"/>
-      <c r="I65" s="1" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="n">
-        <v>58</v>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Утеплённая отмостка, утепление торца плиты, футляры в фундаменте — КР/АР</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr"/>
-      <c r="D66" s="1" t="inlineStr"/>
-      <c r="E66" s="1" t="inlineStr"/>
-      <c r="F66" s="1" t="inlineStr"/>
-      <c r="G66" s="1" t="inlineStr"/>
-      <c r="H66" s="1" t="inlineStr"/>
-      <c r="I66" s="1" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="n">
-        <v>59</v>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Терморегулятор и питание греющего кабеля — ЭОМ</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr"/>
-      <c r="D67" s="1" t="inlineStr"/>
-      <c r="E67" s="1" t="inlineStr"/>
-      <c r="F67" s="1" t="inlineStr"/>
-      <c r="G67" s="1" t="inlineStr"/>
-      <c r="H67" s="1" t="inlineStr"/>
-      <c r="I67" s="1" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Автополив участка от КП-1 — по ландшафтному проекту</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="inlineStr"/>
-      <c r="D68" s="1" t="inlineStr"/>
-      <c r="E68" s="1" t="inlineStr"/>
-      <c r="F68" s="1" t="inlineStr"/>
-      <c r="G68" s="1" t="inlineStr"/>
-      <c r="H68" s="1" t="inlineStr"/>
-      <c r="I68" s="1" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr"/>
-      <c r="B70" t="inlineStr">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
         <is>
           <t>Примечание — Допускается применение оборудования, изделий и материалов других изготовителей с техническими характеристиками не ниже указанных в настоящей спецификации.</t>
         </is>

--- a/ovk-dom-banya/release-nvk/И05.09.26-НВК.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-nvk/И05.09.26-НВК.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -874,12 +874,12 @@
         </is>
       </c>
       <c r="G15" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr">
         <is>
-          <t>В1-Бс: повороты трассы (4) и подъём к колонке КБ (1)</t>
+          <t>В1-Бс: повороты трассы (2) и подъём к колонке КБ (1)</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
         </is>
       </c>
       <c r="G19" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr">
         <is>
-          <t>В1-Бс (18,5 м: зона заезда, перемычка за теплотрассой, над К2-Т и К1-б1 — по 2 м в стороны), КХ-8н на всю длину (2,5 м); лист 3</t>
+          <t>В1-Бс (17,7 м: от КП-1 — зона заезда, над Др-Т, К2-Т и теплотрассой; над К1-б1 — по 2 м в стороны), КХ-8н на всю длину (2,5 м); лист 3</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
         </is>
       </c>
       <c r="G23" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr">
         <is>
-          <t>выпуск К1-1н, линия бани К1-бн, К1-б1 (прямые, без поворотов)</t>
+          <t>выпуск К1-1н, линии бани К1-бн, К1-бвн, К1-б1 (прямые, без поворотов)</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Колодец канализационный полимерный Ø630 с проточным лотком (проход Ø110, перепад 0,02 м), шахтой гофр. Ø400 телескопической, H = 0,87 м, люк Л</t>
+          <t>Колодец канализационный полимерный Ø630 с проточным лотком (два входа Ø110 — К1-б и К1-бв, выход Ø110 к дому), шахтой гофр. Ø400 телескопической, H = 0,87 м, люк Л</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="G26" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H26" s="1" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr"/>
@@ -2038,12 +2038,12 @@
         </is>
       </c>
       <c r="G55" s="1" t="n">
-        <v>113</v>
+        <v>114.5</v>
       </c>
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr">
         <is>
-          <t>основание 100 мм, обсыпка 300 мм; в зоне заезда — на всю глубину (58,3 м³)</t>
+          <t>основание 100 мм, обсыпка 300 мм; в зоне заезда — на всю глубину (58,2 м³)</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="G58" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr">

--- a/ovk-dom-banya/release-nvk/И05.09.26-НВК.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-nvk/И05.09.26-НВК.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="G28" s="1" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr">
@@ -1273,7 +1273,7 @@
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr">
         <is>
-          <t>выпуск КЛ-1 → выпуск ЛК Ø63</t>
+          <t>выпуск КЛ-1 → врезка в существующий выпуск ЛК Ø63 за южной стенкой колодца</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr">
         <is>
-          <t>стык с выпуском ЛК (после шурфа)</t>
+          <t>врезка в существующий выпуск ЛК (после шурфа); участок севернее врезки (≈1,8 м) — демонтаж</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
         </is>
       </c>
       <c r="G31" s="1" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>углы колец и вводов в КЛ-1 (по 2 на угол), транзит, выпуск гаража; выпуски водостоков — по 2</t>
+          <t>углы колец и вводов в КЛ-1 (по 2 на угол), транзит, выпуск гаража, излом Др-К (1); выпуски водостоков — по 2</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="G42" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr">
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="G49" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr">
@@ -2038,12 +2038,12 @@
         </is>
       </c>
       <c r="G55" s="1" t="n">
-        <v>114.5</v>
+        <v>121</v>
       </c>
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr">
         <is>
-          <t>основание 100 мм, обсыпка 300 мм; в зоне заезда — на всю глубину (58,2 м³)</t>
+          <t>основание 100 мм, обсыпка 300 мм; в зоне заезда — на всю глубину (63,7 м³)</t>
         </is>
       </c>
     </row>

--- a/ovk-dom-banya/release-nvk/И05.09.26-НВК.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-nvk/И05.09.26-НВК.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -1330,12 +1330,12 @@
         </is>
       </c>
       <c r="G31" s="1" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>углы колец и вводов в КЛ-1 (по 2 на угол), транзит, выпуск гаража, излом Др-К (1); выпуски водостоков — по 2</t>
+          <t>повороты колец, транзита и подходов к КЛ-1, излом Др-К, выпуск гаража — 15 (по модели); выпуски водостоков — по 2 (16)</t>
         </is>
       </c>
     </row>

--- a/ovk-dom-banya/release-nvk/И05.09.26-НВК.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-nvk/И05.09.26-НВК.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1237,12 +1237,12 @@
         </is>
       </c>
       <c r="G28" s="1" t="n">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>кольца К2 дома и бани, транзит, выпуск лотка гаража</t>
+          <t>кольца К2 дома и бани, транзит, выпуск лотка гаража, подводки от ДК дома (6,9 м) и бани (≈1,2 м, ориентировочно)</t>
         </is>
       </c>
     </row>
@@ -1252,28 +1252,28 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Труба напорная ПЭ 100 SDR17 63×3,8</t>
+          <t>Дождеприёмник пластиковый 300×300 с корзиной-пескоуловителем, боковым входом Ø110 и выходом Ø110, решётка класса A15</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 18599-2001</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr"/>
       <c r="E29" s="1" t="inlineStr"/>
       <c r="F29" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G29" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr">
         <is>
-          <t>выпуск КЛ-1 → врезка в существующий выпуск ЛК Ø63 за южной стенкой колодца</t>
+          <t>ДК-1, ДК-2, ДК-3, ДК-4, ДК-7, ДК-8 (дом); баня — 2, ориентировочно; верх −0,020, лист 5, узел 9</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Муфта электросварная ПЭ 100 Ø63</t>
+          <t>Дождеприёмник пластиковый 300×300 с корзиной-пескоуловителем, боковым входом Ø110 и выходом Ø110, решётка класса C250</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
@@ -1299,12 +1299,12 @@
         </is>
       </c>
       <c r="G30" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr">
         <is>
-          <t>врезка в существующий выпуск ЛК (после шурфа); участок севернее врезки (≈1,8 м) — демонтаж</t>
+          <t>ДК-5, ДК-6 — у ворот гаража и пандуса</t>
         </is>
       </c>
     </row>
@@ -1314,28 +1314,28 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП Ø110, 45°</t>
+          <t>Труба напорная ПЭ 100 SDR17 63×3,8</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 18599-2001</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr"/>
       <c r="E31" s="1" t="inlineStr"/>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G31" s="1" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>повороты колец, транзита и подходов к КЛ-1, излом Др-К, выпуск гаража — 15 (по модели); выпуски водостоков — по 2 (16)</t>
+          <t>выпуск КЛ-1 → врезка в существующий выпуск ЛК Ø63 за южной стенкой колодца</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП Ø110, 90°</t>
+          <t>Муфта электросварная ПЭ 100 Ø63</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
@@ -1361,12 +1361,12 @@
         </is>
       </c>
       <c r="G32" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr">
         <is>
-          <t>слияние полуколец бани, приём транзита бани</t>
+          <t>врезка в существующий выпуск ЛК (после шурфа); участок севернее врезки (≈1,8 м) — демонтаж</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП Ø110 косой 45°</t>
+          <t>Отвод ПП Ø110, 45°</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
@@ -1392,12 +1392,12 @@
         </is>
       </c>
       <c r="G33" s="1" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr">
         <is>
-          <t>выпуски водостоков (8, ориентировочно — по привязке воронок) и лотка гаража</t>
+          <t>повороты колец, транзита и подходов к КЛ-1, излом Др-К, выпуск гаража — 15 (по модели); подводки от ДК к кольцам — по 2 (20: дом 16, баня 4 ориентировочно)</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Футляр (гильза) из трубы ПП Ø160, L = 0,6 м — закладная в край плиты</t>
+          <t>Тройник ПП Ø110, 90°</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
@@ -1423,12 +1423,12 @@
         </is>
       </c>
       <c r="G34" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>выпуски водостоков (узел 9), ориентировочно; закладка — при бетонировании (КР)</t>
+          <t>слияние полуколец бани, приём транзита бани</t>
         </is>
       </c>
     </row>
@@ -1438,12 +1438,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Плита днища ПН15</t>
+          <t>Тройник ПП Ø110 косой 45°</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 8020-2016</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr"/>
@@ -1454,12 +1454,12 @@
         </is>
       </c>
       <c r="G35" s="1" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1 (лист 8, узел 2)</t>
+          <t>врезки подводок от ДК в кольца К2 (дом 8, баня 2 ориентировочно) и выпуск лотка гаража</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Кольцо стеновое КС15.9</t>
+          <t>Плита днища ПН15</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
@@ -1490,7 +1490,7 @@
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1</t>
+          <t>КЛ-1 (лист 8, узел 2)</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Кольцо стеновое КС15.6</t>
+          <t>Кольцо стеновое КС15.9</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Плита перекрытия 1ПП15-1</t>
+          <t>Кольцо стеновое КС15.6</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Кольцо стеновое КС7.3 (горловина)</t>
+          <t>Плита перекрытия 1ПП15-1</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Люк чугунный тяжёлый Т (C250)</t>
+          <t>Кольцо стеновое КС7.3 (горловина)</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 3634-2019</t>
+          <t>ГОСТ 8020-2016</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr"/>
@@ -1614,7 +1614,7 @@
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1 — в зоне заезда</t>
+          <t>КЛ-1</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Скобы ходовые</t>
+          <t>Люк чугунный тяжёлый Т (C250)</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 8020-2016</t>
+          <t>ГОСТ 3634-2019</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr"/>
@@ -1640,12 +1640,12 @@
         </is>
       </c>
       <c r="G41" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1, шаг 0,3 м</t>
+          <t>КЛ-1 — в зоне заезда</t>
         </is>
       </c>
     </row>
@@ -1655,28 +1655,28 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Мастика битумная для наружной гидроизоляции колец, 2 слоя</t>
+          <t>Скобы ходовые</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 8020-2016</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr"/>
       <c r="E42" s="1" t="inlineStr"/>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G42" s="1" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1, наружная поверхность</t>
+          <t>КЛ-1, шаг 0,3 м</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø110</t>
+          <t>Мастика битумная для наружной гидроизоляции колец, 2 слоя</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -1698,16 +1698,16 @@
       <c r="E43" s="1" t="inlineStr"/>
       <c r="F43" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G43" s="1" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1: К2-К, К2-Б, Др-К</t>
+          <t>КЛ-1, наружная поверхность</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø63</t>
+          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø110</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -1733,12 +1733,12 @@
         </is>
       </c>
       <c r="G44" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1: выпуск</t>
+          <t>КЛ-1: К2-К, К2-Б, Др-К</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный канализационный (захлопка) Ø110</t>
+          <t>Уплотнитель (манжета) для ввода трубы в стенку ж/б колодца Ø63</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
@@ -1769,7 +1769,7 @@
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr">
         <is>
-          <t>КЛ-1: вход дренажа Др-К</t>
+          <t>КЛ-1: выпуск</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Решётка-корзина из нержавеющей стали на входе выпуска Ø63</t>
+          <t>Клапан обратный канализационный (захлопка) Ø110</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
@@ -1800,55 +1800,55 @@
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr">
         <is>
+          <t>КЛ-1: вход дренажа Др-К</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Решётка-корзина из нержавеющей стали на входе выпуска Ø63</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="inlineStr"/>
+      <c r="E47" s="1" t="inlineStr"/>
+      <c r="F47" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G47" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="1" t="inlineStr"/>
+      <c r="I47" s="1" t="inlineStr">
+        <is>
           <t>КЛ-1</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr"/>
-      <c r="B47" s="3" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr"/>
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>4. Дренаж Др</t>
         </is>
       </c>
-      <c r="C47" s="1" t="n"/>
-      <c r="D47" s="1" t="n"/>
-      <c r="E47" s="1" t="n"/>
-      <c r="F47" s="1" t="n"/>
-      <c r="G47" s="1" t="n"/>
-      <c r="H47" s="1" t="n"/>
-      <c r="I47" s="1" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Труба дренажная гофрированная перфорированная Ø110 в фильтре из геотекстиля</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>ГОСТ Р 59249-2020 или ТУ изготовителя</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr"/>
-      <c r="E48" s="1" t="inlineStr"/>
-      <c r="F48" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G48" s="1" t="n">
-        <v>150</v>
-      </c>
-      <c r="H48" s="1" t="inlineStr"/>
-      <c r="I48" s="1" t="inlineStr">
-        <is>
-          <t>кольца дренажа дома и бани</t>
-        </is>
-      </c>
+      <c r="C48" s="1" t="n"/>
+      <c r="D48" s="1" t="n"/>
+      <c r="E48" s="1" t="n"/>
+      <c r="F48" s="1" t="n"/>
+      <c r="G48" s="1" t="n"/>
+      <c r="H48" s="1" t="n"/>
+      <c r="I48" s="1" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -1856,12 +1856,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Труба ПП гофрированная двухслойная SN8 Ø110 (без перфорации)</t>
+          <t>Труба дренажная гофрированная перфорированная Ø110 в фильтре из геотекстиля</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32413-2013</t>
+          <t>ГОСТ Р 59249-2020 или ТУ изготовителя</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr"/>
@@ -1872,12 +1872,12 @@
         </is>
       </c>
       <c r="G49" s="1" t="n">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr">
         <is>
-          <t>транзит Др-Т, выход Др-К в КЛ-1</t>
+          <t>кольца дренажа дома и бани</t>
         </is>
       </c>
     </row>
@@ -1887,28 +1887,28 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Колодец дренажный полимерный: шахта гофр. Ø315, днище, крышка</t>
+          <t>Труба ПП гофрированная двухслойная SN8 Ø110 (без перфорации)</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32413-2013</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr"/>
       <c r="E50" s="1" t="inlineStr"/>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G50" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr">
         <is>
-          <t>Др-1…Др-4, ДрБ-1…ДрБ-4 (лист 8, узел 5)</t>
+          <t>транзит Др-Т, выход Др-К в КЛ-1</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная Ø315 для шахт дренажных колодцев</t>
+          <t>Колодец дренажный полимерный: шахта гофр. Ø315, днище, крышка</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
@@ -1930,16 +1930,16 @@
       <c r="E51" s="1" t="inlineStr"/>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G51" s="1" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr">
         <is>
-          <t>H = 1,54…1,79 м, отстойная часть 0,3 м</t>
+          <t>Др-1…Др-4, ДрБ-1…ДрБ-4 (лист 8, узел 5)</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Уплотнитель резиновый для ввода трубы Ø110 в колодец Ø315</t>
+          <t>Труба гофрированная Ø315 для шахт дренажных колодцев</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
@@ -1961,14 +1961,18 @@
       <c r="E52" s="1" t="inlineStr"/>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G52" s="1" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H52" s="1" t="inlineStr"/>
-      <c r="I52" s="1" t="inlineStr"/>
+      <c r="I52" s="1" t="inlineStr">
+        <is>
+          <t>H = 1,54…1,79 м, отстойная часть 0,3 м</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -1976,12 +1980,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Люк чугунный тяжёлый Т (C250) с опорным кольцом для колодца Ø315</t>
+          <t>Уплотнитель резиновый для ввода трубы Ø110 в колодец Ø315</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 3634-2019</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr"/>
@@ -1992,60 +1996,56 @@
         </is>
       </c>
       <c r="G53" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="H53" s="1" t="inlineStr"/>
+      <c r="I53" s="1" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Люк чугунный тяжёлый Т (C250) с опорным кольцом для колодца Ø315</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>ГОСТ 3634-2019</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="inlineStr"/>
+      <c r="E54" s="1" t="inlineStr"/>
+      <c r="F54" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="H53" s="1" t="inlineStr"/>
-      <c r="I53" s="1" t="inlineStr">
+      <c r="H54" s="1" t="inlineStr"/>
+      <c r="I54" s="1" t="inlineStr">
         <is>
           <t>Др-1, Др-3, ДрБ-2, ДрБ-3 — в зоне заезда</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr"/>
-      <c r="B54" s="3" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr"/>
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>5. Материалы траншей и утепление</t>
         </is>
       </c>
-      <c r="C54" s="1" t="n"/>
-      <c r="D54" s="1" t="n"/>
-      <c r="E54" s="1" t="n"/>
-      <c r="F54" s="1" t="n"/>
-      <c r="G54" s="1" t="n"/>
-      <c r="H54" s="1" t="n"/>
-      <c r="I54" s="1" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Песок средней крупности для основания и обсыпки труб и колодцев, засыпки в зоне заезда</t>
-        </is>
-      </c>
-      <c r="C55" s="1" t="inlineStr">
-        <is>
-          <t>ГОСТ 8736-2014</t>
-        </is>
-      </c>
-      <c r="D55" s="1" t="inlineStr"/>
-      <c r="E55" s="1" t="inlineStr"/>
-      <c r="F55" s="1" t="inlineStr">
-        <is>
-          <t>м³</t>
-        </is>
-      </c>
-      <c r="G55" s="1" t="n">
-        <v>121</v>
-      </c>
-      <c r="H55" s="1" t="inlineStr"/>
-      <c r="I55" s="1" t="inlineStr">
-        <is>
-          <t>основание 100 мм, обсыпка 300 мм; в зоне заезда — на всю глубину (63,7 м³)</t>
-        </is>
-      </c>
+      <c r="C55" s="1" t="n"/>
+      <c r="D55" s="1" t="n"/>
+      <c r="E55" s="1" t="n"/>
+      <c r="F55" s="1" t="n"/>
+      <c r="G55" s="1" t="n"/>
+      <c r="H55" s="1" t="n"/>
+      <c r="I55" s="1" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Щебень гранитный фракции 20–40 мм, промытый</t>
+          <t>Песок средней крупности для основания и обсыпки труб и колодцев, засыпки в зоне заезда</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 8267-93</t>
+          <t>ГОСТ 8736-2014</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr"/>
@@ -2069,12 +2069,12 @@
         </is>
       </c>
       <c r="G56" s="1" t="n">
-        <v>33</v>
+        <v>124</v>
       </c>
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr">
         <is>
-          <t>призма вокруг дренажа (узел 8), основание КЛ-1</t>
+          <t>основание 100 мм, обсыпка 300 мм; в зоне заезда — на всю глубину (63,7 м³)</t>
         </is>
       </c>
     </row>
@@ -2084,28 +2084,28 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Геотекстиль иглопробивной 150–200 г/м²</t>
+          <t>Щебень гранитный фракции 20–40 мм, промытый</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 8267-93</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr"/>
       <c r="E57" s="1" t="inlineStr"/>
       <c r="F57" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>м³</t>
         </is>
       </c>
       <c r="G57" s="1" t="n">
-        <v>360</v>
+        <v>33</v>
       </c>
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr">
         <is>
-          <t>обёртка щебня, нахлёст 0,3 м</t>
+          <t>призма вокруг дренажа (узел 8), основание КЛ-1</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Плиты ЭППС 50 мм, плотность не менее 35 кг/м³</t>
+          <t>Геотекстиль иглопробивной 150–200 г/м²</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -2131,46 +2131,60 @@
         </is>
       </c>
       <c r="G58" s="1" t="n">
-        <v>9</v>
+        <v>360</v>
       </c>
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr">
         <is>
+          <t>обёртка щебня, нахлёст 0,3 м</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Плиты ЭППС 50 мм, плотность не менее 35 кг/м³</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="inlineStr"/>
+      <c r="E59" s="1" t="inlineStr"/>
+      <c r="F59" s="1" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="G59" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="H59" s="1" t="inlineStr"/>
+      <c r="I59" s="1" t="inlineStr">
+        <is>
           <t>полоса 1,2 м над трубой на мелких участках (узел 6)</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr"/>
-      <c r="B59" s="3" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr"/>
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>6. Не входит в НВК.СО</t>
         </is>
       </c>
-      <c r="C59" s="1" t="n"/>
-      <c r="D59" s="1" t="n"/>
-      <c r="E59" s="1" t="n"/>
-      <c r="F59" s="1" t="n"/>
-      <c r="G59" s="1" t="n"/>
-      <c r="H59" s="1" t="n"/>
-      <c r="I59" s="1" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Стояки внутренних водостоков в стенах, выпуски К1, ввод В1 и подводка КХ-8 до наружной грани фундамента, лоток гаража ЛГ-1 с пескоуловителем — И05.09.26-ВК.СО</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr"/>
-      <c r="D60" s="1" t="inlineStr"/>
-      <c r="E60" s="1" t="inlineStr"/>
-      <c r="F60" s="1" t="inlineStr"/>
-      <c r="G60" s="1" t="inlineStr"/>
-      <c r="H60" s="1" t="inlineStr"/>
-      <c r="I60" s="1" t="inlineStr"/>
+      <c r="C60" s="1" t="n"/>
+      <c r="D60" s="1" t="n"/>
+      <c r="E60" s="1" t="n"/>
+      <c r="F60" s="1" t="n"/>
+      <c r="G60" s="1" t="n"/>
+      <c r="H60" s="1" t="n"/>
+      <c r="I60" s="1" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -2178,7 +2192,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Утеплённая отмостка, утепление торца плиты, футляры в фундаменте — КР/АР</t>
+          <t>Стояки внутренних водостоков в стенах и их выпуски сквозь стену в ДК (чугун SML), выпуски К1, ввод В1 и подводка КХ-8 до наружной грани фундамента, лоток гаража ЛГ-1 с пескоуловителем — И05.09.26-ВК.СО</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr"/>
@@ -2195,7 +2209,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Терморегулятор и питание греющего кабеля — ЭОМ</t>
+          <t>Утеплённая отмостка, утепление торца плиты, футляры в фундаменте — КР/АР</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr"/>
@@ -2212,7 +2226,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Автополив участка от КП-1 — по ландшафтному проекту</t>
+          <t>Терморегулятор и питание греющего кабеля — ЭОМ</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr"/>
@@ -2223,9 +2237,26 @@
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr"/>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Автополив участка от КП-1 — по ландшафтному проекту</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="inlineStr"/>
+      <c r="D64" s="1" t="inlineStr"/>
+      <c r="E64" s="1" t="inlineStr"/>
+      <c r="F64" s="1" t="inlineStr"/>
+      <c r="G64" s="1" t="inlineStr"/>
+      <c r="H64" s="1" t="inlineStr"/>
+      <c r="I64" s="1" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
         <is>
           <t>Примечание — Допускается применение оборудования, изделий и материалов других изготовителей с техническими характеристиками не ниже указанных в настоящей спецификации.</t>
         </is>

--- a/ovk-dom-banya/release-nvk/И05.09.26-НВК.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-nvk/И05.09.26-НВК.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -1237,12 +1237,12 @@
         </is>
       </c>
       <c r="G28" s="1" t="n">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>кольца К2 дома и бани, транзит, выпуск лотка гаража, подводки от ДК дома (6,9 м) и бани (≈1,2 м, ориентировочно)</t>
+          <t>кольцо К2 дома, ветка К2 бани, транзит, выпуск лотка гаража, подводки от ДК дома (6,9 м) и бани (1,1 м)</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr">
         <is>
-          <t>ДК-1, ДК-2, ДК-3, ДК-4, ДК-7, ДК-8 (дом); баня — 2, ориентировочно; верх −0,020, лист 5, узел 9</t>
+          <t>ДК-1, ДК-2, ДК-3, ДК-4, ДК-7, ДК-8 (дом), ДК-б1, ДК-б2 (баня, наружные водостоки); верх −0,020, лист 5, узел 9</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
         </is>
       </c>
       <c r="G33" s="1" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr">
         <is>
-          <t>повороты колец, транзита и подходов к КЛ-1, излом Др-К, выпуск гаража — 15 (по модели); подводки от ДК к кольцам — по 2 (20: дом 16, баня 4 ориентировочно)</t>
+          <t>повороты кольца дома, ветки бани (в т. ч. ДК-б1 в её начало), транзита и подходов к КЛ-1, излом Др-К, выпуск гаража — 14 (по модели); подводки от ДК — по 2 отвода 45° вниз (20: дом 16, баня 4)</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
         </is>
       </c>
       <c r="G34" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>слияние полуколец бани, приём транзита бани</t>
+          <t>приём транзита К2 бани кольцом дома (Н2)</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
         </is>
       </c>
       <c r="G35" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>врезки подводок от ДК в кольца К2 (дом 8, баня 2 ориентировочно) и выпуск лотка гаража</t>
+          <t>врезки подводок от ДК (дом 8, баня 1) и выпуск лотка гаража</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="G56" s="1" t="n">
-        <v>124</v>
+        <v>119.5</v>
       </c>
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr">
